--- a/files/me-ADPER0000095429.xlsx
+++ b/files/me-ADPER0000095429.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3463-3463</t>
+          <t>3463</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -683,40 +683,40 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>공동체부문 농업환경보전프로그램 대상지 선정기준 개선 및 중요도 조사</t>
+          <t>Development and utilization of agricultural and rural climate information systems to respond to climate crisis</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>배승종, 김수진, 유승환</t>
+          <t>Hayoung Kim, 나라, Dong-Hyuk Joo, Euigeon So, Seung-Hwan Yoo, Seung-Jong Bae, Soo-Jin Kim, Yeong-cheol Kwak, ByeongWoo Choi, K. Park, DalJu Park, YunPyo Lee, MyungWon Lee, YongDuk Shin</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
+          <t>한국기후변화학회지</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>225-231</t>
+          <t>1129-1139</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2025.31.4.225</t>
+          <t>10.15531/ksccr.2025.16.5.1129</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -724,9 +724,7 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L5" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
@@ -738,12 +736,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>농업·농촌 정보체계의 활용도와 접근성에 관한 실증적 분석 - 사업 실무자 설문조사를 중심으로 -</t>
+          <t>공동체부문 농업환경보전프로그램 대상지 선정기준 개선 및 중요도 조사</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>리재웅, 이상현, 유승환, 김진성, 김동중, 취뤼, 이향미</t>
+          <t>배승종, 김수진, 유승환</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -761,17 +759,17 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29-42</t>
+          <t>225-231</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2025.31.4.029</t>
+          <t>10.7851/ksrp.2025.31.4.225</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -793,40 +791,40 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>농업용 저수지의 가능최대홍수량 설계를 위한 하류부 피해 산정 방안 적용성 분석</t>
+          <t>농업·농촌 정보체계의 활용도와 접근성에 관한 실증적 분석 - 사업 실무자 설문조사를 중심으로 -</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>주동혁, 나라, 김하영, 소의건, 송인홍, 이성학, 신길채, 심규현, 허건, 유승환</t>
+          <t>리재웅, 이상현, 유승환, 김진성, 김동중, 취뤼, 이향미</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
+          <t>농촌계획</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59-70</t>
+          <t>29-42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2025.67.3.059</t>
+          <t>10.7851/ksrp.2025.31.4.029</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -834,7 +832,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
@@ -846,12 +846,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>농업용 저수지의 홍수기 운영을 위한 상당강우-저류용량-관리수위 곡선 적용성 분석</t>
+          <t>농업용 저수지의 가능최대홍수량 설계를 위한 하류부 피해 산정 방안 적용성 분석</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>신길채, 나라, 주동혁, 박상빈, 유승환</t>
+          <t>주동혁, 나라, 김하영, 소의건, 송인홍, 이성학, 신길채, 심규현, 허건, 유승환</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -864,22 +864,22 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35-49</t>
+          <t>59-70</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2025.67.4.035</t>
+          <t>10.5389/KSAE.2025.67.3.059</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -899,21 +899,21 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>농업환경보전프로그램 이행점검을 위한 시스템 설계</t>
+          <t>농업용 저수지의 홍수기 운영을 위한 상당강우-저류용량-관리수위 곡선 적용성 분석</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>나라, 주동혁, 유승환, 배승종, 박호철, 최규훈, 성재훈, 최진용, 손정우, 허승오</t>
+          <t>신길채, 나라, 주동혁, 박상빈, 유승환</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
+          <t>한국농공학회논문집</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -922,17 +922,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>55-67</t>
+          <t>35-49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2025.31.4.055</t>
+          <t>10.5389/KSAE.2025.67.4.035</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -940,9 +940,7 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
@@ -954,12 +952,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>농업환경보전프로그램의 농업환경 영향평가를 위한 시스템 개발</t>
+          <t>농업환경보전프로그램 이행점검을 위한 시스템 설계</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>손정우, 허승오, 유승환</t>
+          <t>나라, 주동혁, 유승환, 배승종, 박호철, 최규훈, 성재훈, 최진용, 손정우, 허승오</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -977,17 +975,17 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>215-224</t>
+          <t>55-67</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2025.31.4.215</t>
+          <t>10.7851/ksrp.2025.31.4.055</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1005,55 +1003,53 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>The Application of a Smart Nexus for Agriculture in Korea for Assessing the Holistic Impacts of Climate Change</t>
+          <t>농업환경보전프로그램의 농업환경 영향평가를 위한 시스템 개발</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>라 나, Seung‐Hwan Yoo, Sang‐Hyun Lee, Jin‐Yong Choi, Seung-Oh Hur, Pu Reun Yoon, Kwang Soo Kim</t>
+          <t>손정우, 허승오, 유승환</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Sustainability</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+          <t>농촌계획</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>31</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>990-990</t>
+          <t>215-224</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10.3390/su16030990</t>
+          <t>10.7851/ksrp.2025.31.4.215</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>교신저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr"/>
     </row>
@@ -1062,44 +1058,44 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>K-HAS와 비율보정 계수를 이용한 농업용 저수지의 비상연계 용수공급 가능량 분석</t>
+          <t>Development of a future weather database based on Shared Socioeconomic Pathways scenarios for assessing climate change vulnerability of agricultural infrastructure</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>김하영, 이상현, 나라, 주동혁, 유승환</t>
+          <t>Dong-Hyuk Joo, 나라, Ha-Young Kim, Jaepil Cho, JuHyoung Lee, Suk-ho Song, DalJu Park, , YunPyo Lee, MyoungWon Lee, Seung-Hwan Yoo</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
+          <t>한국기후변화학회지</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>59-71</t>
+          <t>953-964</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2023.65.2.059</t>
+          <t>10.15531/ksccr.2024.15.5.953</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1115,37 +1111,41 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Transboundary water-food nexus based on physical-virtual water embedded in food trade network</t>
+          <t>The Application of a Smart Nexus for Agriculture in Korea for Assessing the Holistic Impacts of Climate Change</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Sang‐Hyun Lee, Makoto Taniguchi, Naoki Masuhara, Seung‐Hwan Yoo, Yun‐Gyeong Oh, Masahiko Haraguchi, Rui Qu</t>
+          <t>라 나, Seung‐Hwan Yoo, Sang‐Hyun Lee, Jin‐Yong Choi, Seung-Oh Hur, Pu Reun Yoon, Kwang Soo Kim</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Journal of Hydrology</t>
+          <t>Sustainability</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>623</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>129819-129819</t>
+          <t>990</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.jhydrol.2023.129819</t>
+          <t>10.3390/su16030990</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M13" s="2" t="inlineStr"/>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>농업용 수로부의 수위 보정을 위한 필터기법별 적용성 분석</t>
+          <t>K-HAS와 비율보정 계수를 이용한 농업용 저수지의 비상연계 용수공급 가능량 분석</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>주동혁, 나라, 김하영, 최규훈, 윤형창, 박상빈, 유승환</t>
+          <t>김하영, 이상현, 나라, 주동혁, 유승환</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1190,22 +1190,22 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51-68</t>
+          <t>59-71</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2023.65.5.051</t>
+          <t>10.5389/KSAE.2023.65.2.059</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1225,48 +1225,48 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>농업용 저수지의 하한 관리 저수율 설정에 따른 농업용수 및 환경용수 공급 가능성 고찰</t>
+          <t>Transboundary water-food nexus based on physical-virtual water embedded in food trade network</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>정지연, 정민혁, 범진아, 박민경, 이재남, 유승환, 윤광식</t>
+          <t>Sang‐Hyun Lee, Makoto Taniguchi, Naoki Masuhara, Seung‐Hwan Yoo, Yun‐Gyeong Oh, Masahiko Haraguchi, Rui Qu</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Journal of Hydrology</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21-33</t>
+          <t>129819</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2023.65.2.021</t>
+          <t>10.1016/j.jhydrol.2023.129819</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
+          <t>교신저자</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="M15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1278,40 +1278,40 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>농업환경보전프로그램 이행단계별 문제점 및 애로사항에 대한 이해당사자별 인식 비교</t>
+          <t>농업용 수로부의 수위 보정을 위한 필터기법별 적용성 분석</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>김수진, 배승종, 유승환, 나라, 손정우, 허승오</t>
+          <t>주동혁, 나라, 김하영, 최규훈, 윤형창, 박상빈, 유승환</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
+          <t>한국농공학회논문집</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>201-210</t>
+          <t>51-68</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2023.29.4.201</t>
+          <t>10.5389/KSAE.2023.65.5.051</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1319,9 +1319,7 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L16" s="2" t="n">
-        <v>2</v>
-      </c>
+      <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1333,12 +1331,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>딥러닝 기법을 이용한 농업용저수지 CCTV 영상 기반의 수위계측 방법 개발</t>
+          <t>농업용 저수지의 하한 관리 저수율 설정에 따른 농업용수 및 환경용수 공급 가능성 고찰</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>주동혁, 이상현, 최규훈, 유승환, 나라, 김하영, 오창조, 윤광식</t>
+          <t>정지연, 정민혁, 범진아, 박민경, 이재남, 유승환, 윤광식</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1351,22 +1349,22 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15-26</t>
+          <t>21-33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2023.65.1.015</t>
+          <t>10.5389/KSAE.2023.65.2.021</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1386,12 +1384,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>물-에너지-식량-탄소 넥서스를 이용한 통합물관리 모델 평가 연구 - 영산강 수계를 중심으로 -</t>
+          <t>농업환경보전프로그램 이행단계별 문제점 및 애로사항에 대한 이해당사자별 인식 비교</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>나라, 박진현, 주동혁, 김하영, 유승환, 오창조, 이상현, 오부영, 허승오</t>
+          <t>김수진, 배승종, 유승환, 나라, 손정우, 허승오</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1404,22 +1402,22 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37-49</t>
+          <t>201-210</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2023.29.1.037</t>
+          <t>10.7851/ksrp.2023.29.4.201</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1428,7 +1426,7 @@
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
     </row>
@@ -1437,42 +1435,44 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Analysis of climate change impact on resource intensity and carbon emissions in protected farming systems using Water-Energy-Food-Carbon Nexus</t>
+          <t>딥러닝 기법을 이용한 농업용저수지 CCTV 영상 기반의 수위계측 방법 개발</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Pu Reun Yoon, Sang‐Hyun Lee, Jin‐Yong Choi, Seung‐Hwan Yoo, Seung-Oh Hur</t>
+          <t>주동혁, 이상현, 최규훈, 유승환, 나라, 김하영, 오창조, 윤광식</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Resources Conservation and Recycling</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>106394-106394</t>
+          <t>15-26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.resconrec.2022.106394</t>
+          <t>10.5389/KSAE.2023.65.1.015</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1480,9 +1480,7 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L19" s="2" t="n">
-        <v>62</v>
-      </c>
+      <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1490,55 +1488,53 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Development of WEF-P Nexus based on product-supply chain: A case study of phosphorous fertilizer industry in Morocco</t>
+          <t>물-에너지-식량-탄소 넥서스를 이용한 통합물관리 모델 평가 연구 - 영산강 수계를 중심으로 -</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Sang‐Hyun Lee, Amjad T. Assi, Rabi H. Mohtar, Meryem Hamane, Pu Reun Yoon, Seung‐Hwan Yoo</t>
+          <t>나라, 박진현, 주동혁, 김하영, 유승환, 오창조, 이상현, 오부영, 허승오</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>The Science of The Total Environment</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>857</t>
-        </is>
+          <t>농촌계획</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>29</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Pt 2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>159520-159520</t>
+          <t>37-49</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.scitotenv.2022.159520</t>
+          <t>10.7851/ksrp.2023.29.1.037</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>교신저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr"/>
     </row>
@@ -1551,40 +1547,38 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>농업경영체 등록정보와 공간정보를 활용한 농지범용화 사업 대상지 선정 방안 개발 및 적용</t>
+          <t>Analysis of climate change impact on resource intensity and carbon emissions in protected farming systems using Water-Energy-Food-Carbon Nexus</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>나라, 주동혁, 김하영, 유승환, 곽영철, 김정훈, 이향미, 조은정</t>
+          <t>Pu Reun Yoon, Sang‐Hyun Lee, Jin‐Yong Choi, Seung‐Hwan Yoo, Seung-Oh Hur</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Resources Conservation and Recycling</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17-26</t>
+          <t>106394</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2022.28.1.017</t>
+          <t>10.1016/j.resconrec.2022.106394</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1593,7 +1587,7 @@
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
     </row>
@@ -1606,48 +1600,52 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>농업용저수지의 실시간 수위 보정을 위한 Hampel Filter의 최적 Window Size 분석</t>
+          <t>Development of WEF-P Nexus based on product-supply chain: A case study of phosphorous fertilizer industry in Morocco</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>주동혁, 나라, 김하영, 최규훈, 권재환, 유승환</t>
+          <t>Sang‐Hyun Lee, Amjad T. Assi, Rabi H. Mohtar, Meryem Hamane, Pu Reun Yoon, Seung‐Hwan Yoo</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>64</v>
+          <t>The Science of The Total Environment</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Pt 2</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9-24</t>
+          <t>159520</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2022.64.3.009</t>
+          <t>10.1016/j.scitotenv.2022.159520</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr"/>
+          <t>교신저자</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>19</v>
+      </c>
       <c r="M22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1659,40 +1657,40 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>설계강우의 지속시간 및 시간분포에 따른 배수개선 농경지 침수 영향 분석</t>
+          <t>농업경영체 등록정보와 공간정보를 활용한 농지범용화 사업 대상지 선정 방안 개발 및 적용</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>전상민, 김귀훈, 이현지, 강기호, 유승환, 최진용, 강문성</t>
+          <t>나라, 주동혁, 김하영, 유승환, 곽영철, 김정훈, 이향미, 조은정</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
+          <t>농촌계획</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47-55</t>
+          <t>17-26</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2022.64.2.047</t>
+          <t>10.7851/ksrp.2022.28.1.017</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1700,7 +1698,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1708,52 +1708,52 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Analysis of industrial water–energy–labor nexus zones for economic and resource-based impact assessment</t>
+          <t>농업용저수지의 실시간 수위 보정을 위한 Hampel Filter의 최적 Window Size 분석</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Sang‐Hyun Lee, Makoto Taniguchi, Naoki Masuhara, Rabi H. Mohtar, Seung‐Hwan Yoo, Masahiko Haraguchi</t>
+          <t>주동혁, 나라, 김하영, 최규훈, 권재환, 유승환</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Resources Conservation and Recycling</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>105483-105483</t>
+          <t>9-24</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.resconrec.2021.105483</t>
+          <t>10.5389/KSAE.2022.64.3.009</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>교신저자</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>19</v>
-      </c>
+          <t>공저자</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1761,46 +1761,44 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Assessing the Potential of Agricultural Reservoirs as the Source of Environmental Flow</t>
+          <t>설계강우의 지속시간 및 시간분포에 따른 배수개선 농경지 침수 영향 분석</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Young-Jun Jo, Jung‐Hun Song, Younggu Her, Giorgio Provolo, Jina Beom, Minhyuk Jeung, Young‐Joo Kim, Seung‐Hwan Yoo, Kwang‐Sik Yoon</t>
+          <t>전상민, 김귀훈, 이현지, 강기호, 유승환, 최진용, 강문성</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Water</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>64</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>508-508</t>
+          <t>47-55</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10.3390/w13040508</t>
+          <t>10.5389/KSAE.2022.64.2.047</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1808,9 +1806,7 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L25" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1822,51 +1818,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Evaluation of Irrigation Safety by Operation Management of Water Supply from Large Scale Agricultural Reservoirs</t>
+          <t>Analysis of industrial water–energy–labor nexus zones for economic and resource-based impact assessment</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Minhyuk Jeung, Jina Beom, Mu-hong Sung, Jaenam Lee, Seung‐Hwan Yoo, Kwang-sik Yoon</t>
+          <t>Sang‐Hyun Lee, Makoto Taniguchi, Naoki Masuhara, Rabi H. Mohtar, Seung‐Hwan Yoo, Masahiko Haraguchi</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Korean Society of Hazard Mitigation</t>
+          <t>Resources Conservation and Recycling</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>189-198</t>
+          <t>105483</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10.9798/kosham.2021.21.1.189</t>
+          <t>10.1016/j.resconrec.2021.105483</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>교신저자</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="M26" s="2" t="inlineStr"/>
     </row>
@@ -1879,38 +1871,42 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Policy assessment of Agricultural Infrastructure Improvement Project for Preliminary Feasibility Study- Multipurpose Rural Water Development Project in Pangyo District -</t>
+          <t>Assessing the Potential of Agricultural Reservoirs as the Source of Environmental Flow</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Soo Jin Kim, Seung Jong Bae, Yoo SeungHwan, Yoonhyung Kim, Sungeun Yoon, Jeong‐Hoon Kim</t>
+          <t>Young-Jun Jo, Jung‐Hun Song, Younggu Her, Giorgio Provolo, Jina Beom, Minhyuk Jeung, Young‐Joo Kim, Seung‐Hwan Yoo, Kwang‐Sik Yoon</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Journal of Korean Society of Rural Planning</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>21-28</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>10.3390/w13040508</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1919,7 +1915,7 @@
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M27" s="2" t="inlineStr"/>
     </row>
@@ -1932,38 +1928,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Vulnerability assessment of rural aging community for abandoned farmlands in South Korea</t>
+          <t>Evaluation of Irrigation Safety by Operation Management of Water Supply from Large Scale Agricultural Reservoirs</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Jimin Lee, Yun‐Gyeong Oh, Seung‐Hwan Yoo, Kyo Suh</t>
+          <t>Minhyuk Jeung, Jina Beom, Mu-hong Sung, Jaenam Lee, Seung‐Hwan Yoo, Kwang-sik Yoon</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Land Use Policy</t>
+          <t>Korean Society of Hazard Mitigation</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>105544-105544</t>
+          <t>189-198</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.landusepol.2021.105544</t>
+          <t>10.9798/kosham.2021.21.1.189</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>국내 기타</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr"/>
     </row>
@@ -1985,40 +1985,38 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>농업생산기반정비사업의 예비타당성조사 정책효과 분석 - 판교지구 다목적 농촌용수개발사업을 중심으로 -</t>
+          <t>Vulnerability assessment of rural aging community for abandoned farmlands in South Korea</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>김수진, 배승종, 유승환, 김윤형, 윤성은, 김정훈</t>
+          <t>Jimin Lee, Yun‐Gyeong Oh, Seung‐Hwan Yoo, Kyo Suh</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Land Use Policy</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21-28</t>
+          <t>105544</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2021.27.1.021</t>
+          <t>10.1016/j.landusepol.2021.105544</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2027,7 +2025,7 @@
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M29" s="2" t="inlineStr"/>
     </row>
@@ -2040,40 +2038,40 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>농업용 저수지의 농업가뭄에 대한 기후변화 잠재영향 평가</t>
+          <t>농업생산기반정비사업의 예비타당성조사 정책효과 분석 - 판교지구 다목적 농촌용수개발사업을 중심으로 -</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>김수진, 황세운, 배승종, 유승환, 최진용, 장민원</t>
+          <t>김수진, 배승종, 유승환, 김윤형, 윤성은, 김정훈</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
+          <t>농촌계획</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>141-150</t>
+          <t>21-28</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2021.63.6.141</t>
+          <t>10.7851/ksrp.2021.27.1.021</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2081,7 +2079,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
@@ -2093,12 +2093,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>대규모 농업용저수지 수혜면적 변화에 따른 효율적 용수재분배 모의</t>
+          <t>농업용 저수지의 농업가뭄에 대한 기후변화 잠재영향 평가</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>성무홍, 정민혁, 범진아, 박태선, 이재남, 정형모, 김영주, 유승환, 윤광식</t>
+          <t>김수진, 황세운, 배승종, 유승환, 최진용, 장민원</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2111,22 +2111,22 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1-12</t>
+          <t>141-150</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2021.63.3.001</t>
+          <t>10.5389/KSAE.2021.63.6.141</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2134,9 +2134,7 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L31" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
@@ -2148,12 +2146,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>수리·수문설계시스템 및 비율보정계수 기법을 활용한 농업용 저수지의 홍수기 운영기준 평가</t>
+          <t>대규모 농업용저수지 수혜면적 변화에 따른 효율적 용수재분배 모의</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>정형모, 이상현, 김경환, 곽영철, 최은혁, 윤성은, 나라, 주동혁, 유승환, 윤광식</t>
+          <t>성무홍, 정민혁, 범진아, 박태선, 이재남, 정형모, 김영주, 유승환, 윤광식</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2166,22 +2164,22 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>97-104</t>
+          <t>1-12</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2021.63.4.097</t>
+          <t>10.5389/KSAE.2021.63.3.001</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2190,7 +2188,7 @@
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr"/>
     </row>
@@ -2203,12 +2201,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>필터링 기법을 이용한 농업용저수지 수위자료의 품질관리 방안</t>
+          <t>수리·수문설계시스템 및 비율보정계수 기법을 활용한 농업용 저수지의 홍수기 운영기준 평가</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>김경환, 최규훈, 정형모, 주동혁, 나라, 최은혁, 권재환, 유승환</t>
+          <t>정형모, 이상현, 김경환, 곽영철, 최은혁, 윤성은, 나라, 주동혁, 유승환, 윤광식</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2221,22 +2219,22 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>83-93</t>
+          <t>97-104</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2021.63.5.083</t>
+          <t>10.5389/KSAE.2021.63.4.097</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2244,7 +2242,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="M33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
@@ -2252,56 +2252,52 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>A Proposal of Start-up Education Program for Designer</t>
+          <t>필터링 기법을 이용한 농업용저수지 수위자료의 품질관리 방안</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Seung Hwan Yoo, Bo Hyeon Yoo</t>
+          <t>김경환, 최규훈, 정형모, 주동혁, 나라, 최은혁, 권재환, 유승환</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Journal of Cultural Product &amp; Design</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>63</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>73-82</t>
+          <t>83-93</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10.18555/kicpd.2020.63.07</t>
+          <t>10.5389/KSAE.2021.63.5.083</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>주저자</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>0</v>
-      </c>
+          <t>공저자</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
@@ -2313,37 +2309,37 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Assessing the Resilience of Agricultural Reservoirs in Ungauged Catchments under Climate Change Using a Ratio Correction Factors-Based Calibration and Run Theory</t>
+          <t>A Proposal of Start-up Education Program for Designer</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Sang‐Hyun Lee, Sungtae Shin, Jin‐Yong Choi, Jihoon Park, Seung‐Hwan Yoo</t>
+          <t>Seung Hwan Yoo, Bo Hyeon Yoo</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Journal of Cultural Product &amp; Design</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>63</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1618-1618</t>
+          <t>73-82</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10.3390/w12061618</t>
+          <t>10.18555/kicpd.2020.63.07</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2353,11 +2349,11 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>교신저자</t>
+          <t>주저자</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr"/>
     </row>
@@ -2370,12 +2366,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Evaluating the Impact of Climate Change on Paddy Water Balance Using APEX-Paddy Model</t>
+          <t>Assessing the Resilience of Agricultural Reservoirs in Ungauged Catchments under Climate Change Using a Ratio Correction Factors-Based Calibration and Run Theory</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Mohammad Kamruzzaman, Syewoon Hwang, Soon-Kun Choi, Jaepil Cho, Inhong Song, Jung‐Hun Song, Hanseok Jeong, Taeil Jang, Seung‐Hwan Yoo</t>
+          <t>Sang‐Hyun Lee, Sungtae Shin, Jin‐Yong Choi, Jihoon Park, Seung‐Hwan Yoo</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2390,17 +2386,17 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>852-852</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>10.3390/w12030852</t>
+          <t>10.3390/w12061618</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2410,11 +2406,11 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>교신저자</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
     </row>
@@ -2427,33 +2423,37 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Food-centric interlinkages in agricultural food-energy-water nexus under climate change and irrigation management</t>
+          <t>Evaluating the Impact of Climate Change on Paddy Water Balance Using APEX-Paddy Model</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Sang‐Hyun Lee, Jin‐Yong Choi, Seung-Oh Hur, Makoto Taniguchi, Naoki Masuhara, Kwang Soo Kim, Shinwoo Hyun, Eunhee Choi, Jae-hoon Sung, Seung‐Hwan Yoo</t>
+          <t>Mohammad Kamruzzaman, Syewoon Hwang, Soon-Kun Choi, Jaepil Cho, Inhong Song, Jung‐Hun Song, Hanseok Jeong, Taeil Jang, Seung‐Hwan Yoo</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Resources Conservation and Recycling</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>105099-105099</t>
+          <t>852</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.resconrec.2020.105099</t>
+          <t>10.3390/w12030852</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2463,11 +2463,11 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>교신저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="M37" s="2" t="inlineStr"/>
     </row>
@@ -2480,33 +2480,33 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Prediction of the effects of management practices on discharge and mineral nitrogen yield from paddy fields under future climate using APEX-paddy model</t>
+          <t>Food-centric interlinkages in agricultural food-energy-water nexus under climate change and irrigation management</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Mohammad Kamruzzaman, Syewoon Hwang, Soon-Kun Choi, Jaepil Cho, Inhong Song, Hanseok Jeong, Jung‐Hun Song, Teail Jang, Seung‐Hwan Yoo</t>
+          <t>Sang‐Hyun Lee, Jin‐Yong Choi, Seung-Oh Hur, Makoto Taniguchi, Naoki Masuhara, Kwang Soo Kim, Shinwoo Hyun, Eunhee Choi, Jae-hoon Sung, Seung‐Hwan Yoo</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Agricultural Water Management</t>
+          <t>Resources Conservation and Recycling</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>163</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>106345-106345</t>
+          <t>105099</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.agwat.2020.106345</t>
+          <t>10.1016/j.resconrec.2020.105099</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>교신저자</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="M38" s="2" t="inlineStr"/>
     </row>
@@ -2533,40 +2533,38 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>가뭄 대응형 지하수 개발 우선순위 선정을 위한 농촌용수구역의 유형 분석</t>
+          <t>Prediction of the effects of management practices on discharge and mineral nitrogen yield from paddy fields under future climate using APEX-paddy model</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>오윤경, 이상현, 김아라, 홍순욱, 유승환</t>
+          <t>Mohammad Kamruzzaman, Syewoon Hwang, Soon-Kun Choi, Jaepil Cho, Inhong Song, Hanseok Jeong, Jung‐Hun Song, Teail Jang, Seung‐Hwan Yoo</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Agricultural Water Management</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>51-59</t>
+          <t>106345</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>10.7851/Ksrp.2020.26.2.051</t>
+          <t>10.1016/j.agwat.2020.106345</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2575,7 +2573,7 @@
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M39" s="2" t="inlineStr"/>
     </row>
@@ -2588,12 +2586,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>기후변화에 따른 농업생산기반시설 영향분석을 통한 정책추진 방안 연구</t>
+          <t>가뭄 대응형 지하수 개발 우선순위 선정을 위한 농촌용수구역의 유형 분석</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>정경훈, 송석호, 정형모, 오승헌, 김수진, 임세윤, 주동혁, 황세운, 장민원, 배승종, 유승환</t>
+          <t>오윤경, 이상현, 김아라, 홍순욱, 유승환</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2606,22 +2604,22 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>81-91</t>
+          <t>51-59</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2020.26.4.081</t>
+          <t>10.7851/Ksrp.2020.26.2.051</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2630,7 +2628,7 @@
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr"/>
     </row>
@@ -2643,40 +2641,40 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>미래 수요예측을 통한 제주도 농업용수 회복탄력적 공급 방안에 관한 연구</t>
+          <t>기후변화에 따른 농업생산기반시설 영향분석을 통한 정책추진 방안 연구</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>고재한, 정민혁, 범진아, 성무홍, 정형모, 유승환, 윤광식</t>
+          <t>정경훈, 송석호, 정형모, 오승헌, 김수진, 임세윤, 주동혁, 황세운, 장민원, 배승종, 유승환</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
+          <t>농촌계획</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>71-83</t>
+          <t>81-91</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2020.62.3.071</t>
+          <t>10.7851/ksrp.2020.26.4.081</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2684,7 +2682,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="M41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
@@ -2696,38 +2696,40 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>한국조사연구학회 발표 논문 내용분석, 1999∼2019년: 학문분야ㆍ방법론ㆍ연구대상ㆍ데이터분석기법의 지속과 변동</t>
+          <t>미래 수요예측을 통한 제주도 농업용수 회복탄력적 공급 방안에 관한 연구</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Dong-Hoon Seol, 고재훈, 유승환, 이기재</t>
+          <t>고재한, 정민혁, 범진아, 성무홍, 정형모, 유승환, 윤광식</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>조사연구</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>62</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1-32</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
+          <t>71-83</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>10.5389/KSAE.2020.62.3.071</t>
+        </is>
+      </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2735,9 +2737,7 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L42" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
@@ -2745,26 +2745,26 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Assessment of food trade impacts on water, food, and land security in the MENA region</t>
+          <t>한국조사연구학회 발표 논문 내용분석, 1999∼2019년: 학문분야ㆍ방법론ㆍ연구대상ㆍ데이터분석기법의 지속과 변동</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Sang‐Hyun Lee, Rabi H. Mohtar, Seung‐Hwan Yoo</t>
+          <t>Dong-Hoon Seol, 고재훈, 유승환, 이기재</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Hydrology and earth system sciences</t>
+          <t>조사연구</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -2774,26 +2774,22 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>557-572</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>10.5194/hess-23-557-2019</t>
-        </is>
-      </c>
+          <t>1-32</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>국내 기타</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>교신저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr"/>
     </row>
@@ -2806,22 +2802,22 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Uncertainty in hydrological analysis of climate change: multi-parameter vs. multi-GCM ensemble predictions</t>
+          <t>Assessment of food trade impacts on water, food, and land security in the MENA region</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Younggu Her, Seung‐Hwan Yoo, Jaepil Cho, Syewoon Hwang, Jaehak Jeong, Chounghyun Seong</t>
+          <t>Sang‐Hyun Lee, Rabi H. Mohtar, Seung‐Hwan Yoo</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Scientific Reports</t>
+          <t>Hydrology and earth system sciences</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -2831,12 +2827,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>4974-4974</t>
+          <t>557-572</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>10.1038/s41598-019-41334-7</t>
+          <t>10.5194/hess-23-557-2019</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -2850,7 +2846,7 @@
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>303</v>
+        <v>56</v>
       </c>
       <c r="M44" s="2" t="inlineStr"/>
     </row>
@@ -2863,49 +2859,51 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>기후변화 대응을 위한 양수장의 농업가뭄 취약성 실태 평가</t>
+          <t>Uncertainty in hydrological analysis of climate change: multi-parameter vs. multi-GCM ensemble predictions</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>장민원, 김수진, 배승종, 유승환, 정경훈, 황세운</t>
+          <t>Younggu Her, Seung‐Hwan Yoo, Jaepil Cho, Syewoon Hwang, Jaehak Jeong, Chounghyun Seong</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>61</v>
+          <t>Scientific Reports</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>31-40</t>
+          <t>4974</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2019.61.6.031</t>
+          <t>10.1038/s41598-019-41334-7</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>교신저자</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0</v>
+        <v>286</v>
       </c>
       <c r="M45" s="2" t="inlineStr"/>
     </row>
@@ -2918,12 +2916,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>농업용저수지를 이용한 환경생태유량 확보방안 경제성 비교 연구 - 동복천을 중심으로 -</t>
+          <t>기후변화 대응을 위한 양수장의 농업가뭄 취약성 실태 평가</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>박진현, 고재한, 성무홍, 정형모, 박태선, 곽영철, 최우영, 범진아, 정민혁, 유승환, 윤광식</t>
+          <t>장민원, 김수진, 배승종, 유승환, 정경훈, 황세운</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2936,22 +2934,22 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>33-47</t>
+          <t>31-40</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2019.61.5.033</t>
+          <t>10.5389/KSAE.2019.61.6.031</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2959,7 +2957,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
@@ -2967,56 +2967,52 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>An Analysis of the Water-Energy-Food-Land Requirements and CO2 Emissions for Food Security of Rice in Japan</t>
+          <t>농업용저수지를 이용한 환경생태유량 확보방안 경제성 비교 연구 - 동복천을 중심으로 -</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Sang‐Hyun Lee, Makoto Taniguchi, Rabi H. Mohtar, Jin‐Yong Choi, Seung‐Hwan Yoo</t>
+          <t>박진현, 고재한, 성무홍, 정형모, 박태선, 곽영철, 최우영, 범진아, 정민혁, 유승환, 윤광식</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Sustainability</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>61</v>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>3354-3354</t>
+          <t>33-47</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>10.3390/su10093354</t>
+          <t>10.5389/KSAE.2019.61.5.033</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>교신저자</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>32</v>
-      </c>
+          <t>공저자</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
@@ -3028,17 +3024,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Analysis of Drought Intensity and Trends Using the Modified SPEI in South Korea from 1981 to 2010</t>
+          <t>An Analysis of the Water-Energy-Food-Land Requirements and CO2 Emissions for Food Security of Rice in Japan</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Seung-Jong Bae, Sang Hyun Lee, Seung-Hwan Yoo, Tae‐Gon Kim</t>
+          <t>Sang‐Hyun Lee, Makoto Taniguchi, Rabi H. Mohtar, Jin‐Yong Choi, Seung‐Hwan Yoo</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Sustainability</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -3048,17 +3044,17 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>327-327</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>10.3390/w10030327</t>
+          <t>10.3390/su10093354</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -3068,11 +3064,11 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>교신저자</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="M48" s="2" t="inlineStr"/>
     </row>
@@ -3085,37 +3081,37 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Water footprint for Korean rice products and virtual water trade in a water-energy-food nexus</t>
+          <t>Analysis of Drought Intensity and Trends Using the Modified SPEI in South Korea from 1981 to 2010</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Sang‐Hyun Lee, Jin‐Yong Choi, Seung‐Hwan Yoo, Rabi H. Mohtar</t>
+          <t>Seung-Jong Bae, Sang Hyun Lee, Seung-Hwan Yoo, Tae‐Gon Kim</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Water International</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>871-886</t>
+          <t>327</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>10.1080/02508060.2018.1515570</t>
+          <t>10.3390/w10030327</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -3129,7 +3125,7 @@
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="M49" s="2" t="inlineStr"/>
     </row>
@@ -3142,40 +3138,42 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>농어촌용수 및 농업생산기반시설의 실태조사에 따른 기후변화 영향 분석</t>
+          <t>Water footprint for Korean rice products and virtual water trade in a water-energy-food nexus</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>김수진, 배승종, 최진용, 김성필, 은상규, 유승환, 장태일, 고남영, 황세운, 김성준, 박태선, 정경훈, 송석호</t>
+          <t>Sang‐Hyun Lee, Jin‐Yong Choi, Seung‐Hwan Yoo, Rabi H. Mohtar</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>60</v>
+          <t>Water International</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>1-15</t>
+          <t>871-886</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2018.60.5.001</t>
+          <t>10.1080/02508060.2018.1515570</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -3184,7 +3182,7 @@
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M50" s="2" t="inlineStr"/>
     </row>
@@ -3197,12 +3195,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>농업경영체 등록정보를 활용한 밭 경작지의 공간적 파편화 특성 분석</t>
+          <t>농어촌용수 및 농업생산기반시설의 실태조사에 따른 기후변화 영향 분석</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>이지민, 유승환, 오윤경</t>
+          <t>김수진, 배승종, 최진용, 김성필, 은상규, 유승환, 장태일, 고남영, 황세운, 김성준, 박태선, 정경훈, 송석호</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3215,22 +3213,22 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>13-24</t>
+          <t>1-15</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2018.60.2.013</t>
+          <t>10.5389/KSAE.2018.60.5.001</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -3238,7 +3236,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>농업경영체 등록정보와 공간데이터를 활용한 밭 이용 방안 연구: 전라남도 무안군·해남군을 중심으로</t>
+          <t>농업경영체 등록정보를 활용한 밭 경작지의 공간적 파편화 특성 분석</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>오윤경, 유승환, 최수명, 이지민</t>
+          <t>이지민, 유승환, 오윤경</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3268,22 +3268,22 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>27-35</t>
+          <t>13-24</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2018.60.4.027</t>
+          <t>10.5389/KSAE.2018.60.2.013</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -3291,9 +3291,7 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L52" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
@@ -3305,12 +3303,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>물-에너지-식량-토지 넥서스를 통한 미래 쌀 수급 변화에 따른 자원별 이용량 변화 분석</t>
+          <t>농업경영체 등록정보와 공간데이터를 활용한 밭 이용 방안 연구: 전라남도 무안군·해남군을 중심으로</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>이상현, 최진용, 유승환, 허승오</t>
+          <t>오윤경, 유승환, 최수명, 이지민</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3328,17 +3326,17 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>93-103</t>
+          <t>27-35</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2018.60.4.093</t>
+          <t>10.5389/KSAE.2018.60.4.027</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -3347,7 +3345,7 @@
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr"/>
     </row>
@@ -3360,12 +3358,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>지형 특성과 경작지 분포를 고려한 밭정비 유형 분석 - 무안군과 화순군 비교 -</t>
+          <t>물-에너지-식량-토지 넥서스를 통한 미래 쌀 수급 변화에 따른 자원별 이용량 변화 분석</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>이지민, 유승환, 오윤경, 김아라</t>
+          <t>이상현, 최진용, 유승환, 허승오</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3378,22 +3376,22 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>133-144</t>
+          <t>93-103</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2018.60.6.133</t>
+          <t>10.5389/KSAE.2018.60.4.093</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -3401,7 +3399,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="M54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>회복탄력성을 고려한 기상 시나리오별 가뭄 용수 공급방안: 나주호를 중심으로</t>
+          <t>지형 특성과 경작지 분포를 고려한 밭정비 유형 분석 - 무안군과 화순군 비교 -</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>박진현, 고재한, 조영준, 정경훈, 성무홍, 정형모, 박현규, 유승환, 윤광식</t>
+          <t>이지민, 유승환, 오윤경, 김아라</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3431,22 +3431,22 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>115-124</t>
+          <t>133-144</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2018.60.5.115</t>
+          <t>10.5389/KSAE.2018.60.6.133</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -3454,9 +3454,7 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L55" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
@@ -3464,55 +3462,53 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Assessment of the Impact of Climate Change on Drought Characteristics in the Hwanghae Plain, North Korea Using Time Series SPI and SPEI: 1981–2100</t>
+          <t>회복탄력성을 고려한 기상 시나리오별 가뭄 용수 공급방안: 나주호를 중심으로</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Sanghyun Lee, Seung‐Hwan Yoo, Jin‐Yong Choi, Seung-Jong Bae</t>
+          <t>박진현, 고재한, 조영준, 정경훈, 성무홍, 정형모, 박현규, 유승환, 윤광식</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Water</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>60</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>579-579</t>
+          <t>115-124</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>10.3390/w9080579</t>
+          <t>10.5389/KSAE.2018.60.5.115</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>교신저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>112</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr"/>
     </row>
@@ -3525,37 +3521,37 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Extension of Typical Meteorological Data and Energy Demand Analysis for Building Energy Efficiency Rating Certification System</t>
+          <t>Assessment of the Impact of Climate Change on Drought Characteristics in the Hwanghae Plain, North Korea Using Time Series SPI and SPEI: 1981–2100</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Sung Lee, Jonghun Kim, Hakgeun Jeong, Seung‐Hwan Yoo, Jung Hun Lee</t>
+          <t>Sanghyun Lee, Seung‐Hwan Yoo, Jin‐Yong Choi, Seung-Jong Bae</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>KIEAE Journal</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>13-20</t>
+          <t>579</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>10.12813/kieae.2017.17.2.013</t>
+          <t>10.3390/w9080579</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3565,11 +3561,11 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>교신저자</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="M57" s="2" t="inlineStr"/>
     </row>
@@ -3582,37 +3578,37 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>GCM‐related uncertainty in forecasting irrigation and design water requirement for paddy rice fields</t>
+          <t>Extension of Typical Meteorological Data and Energy Demand Analysis for Building Energy Efficiency Rating Certification System</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Sang‐Hyun Lee, 승환 유, Jin‐Yong Choi, Syewoon Hwang</t>
+          <t>Sung Lee, Jonghun Kim, Hakgeun Jeong, Seung‐Hwan Yoo, Jung Hun Lee</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>International Journal of Climatology</t>
+          <t>KIEAE Journal</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>1298-1313</t>
+          <t>13-20</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>10.1002/joc.5244</t>
+          <t>10.12813/kieae.2017.17.2.013</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -3622,11 +3618,11 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>교신저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr"/>
     </row>
@@ -3639,22 +3635,22 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Nonparametric quantile mapping using the response surface method – bias correction of daily precipitation</t>
+          <t>GCM‐related uncertainty in forecasting irrigation and design water requirement for paddy rice fields</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Taeho Bong, Younghwan Son, Seung‐Hwan Yoo, Syewoon Hwang</t>
+          <t>Sang‐Hyun Lee, 승환 유, Jin‐Yong Choi, Syewoon Hwang</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Journal of Water and Climate Change</t>
+          <t>International Journal of Climatology</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>38</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -3664,12 +3660,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>525-539</t>
+          <t>1298-1313</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>10.2166/wcc.2017.127</t>
+          <t>10.1002/joc.5244</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -3679,11 +3675,11 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>교신저자</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M59" s="2" t="inlineStr"/>
     </row>
@@ -3696,17 +3692,17 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>The effect of plasma on shear bond strength between resin cement and colored zirconia</t>
+          <t>Nonparametric quantile mapping using the response surface method – bias correction of daily precipitation</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Chan Park, Seung-Hwan Yoo, Sang-Won Park, Kwi‐Dug Yun, Min-Kyung Ji, Jin-Ho Shin, Hyun‐Pil Lim</t>
+          <t>Taeho Bong, Younghwan Son, Seung‐Hwan Yoo, Syewoon Hwang</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>The Journal of Advanced Prosthodontics</t>
+          <t>Journal of Water and Climate Change</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -3716,22 +3712,22 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>118-118</t>
+          <t>525-539</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>10.4047/jap.2017.9.2.118</t>
+          <t>10.2166/wcc.2017.127</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3740,7 +3736,7 @@
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="M60" s="2" t="inlineStr"/>
     </row>
@@ -3753,40 +3749,42 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>경제성 지표를 활용한 농업용저수지의 생활용수 공급가능성 평가</t>
+          <t>The effect of plasma on shear bond strength between resin cement and colored zirconia</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>윤광식, 최수명, 채종훈, 유승환, 최동호, 윤석군, 이창희, 정경훈, 신길채</t>
+          <t>Chan Park, Seung-Hwan Yoo, Sang-Won Park, Kwi‐Dug Yun, Min-Kyung Ji, Jin-Ho Shin, Hyun‐Pil Lim</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="n">
-        <v>23</v>
+          <t>The Journal of Advanced Prosthodontics</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>85-96</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2017.23.1.085</t>
+          <t>10.4047/jap.2017.9.2.118</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>국내 기타</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3795,7 +3793,7 @@
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M61" s="2" t="inlineStr"/>
     </row>
@@ -3804,55 +3802,53 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Analysis of the characteristics of the global virtual water trade network using degree and eigenvector centrality, with a focus on food and feed crops</t>
+          <t>경제성 지표를 활용한 농업용저수지의 생활용수 공급가능성 평가</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Sang‐Hyun Lee, Rabi H. Mohtar, Jin‐Yong Choi, Seung‐Hwan Yoo</t>
+          <t>윤광식, 최수명, 채종훈, 유승환, 최동호, 윤석군, 이창희, 정경훈, 신길채</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Hydrology and earth system sciences</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+          <t>농촌계획</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>23</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>4223-4235</t>
+          <t>85-96</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>10.5194/hess-20-4223-2016</t>
+          <t>10.7851/ksrp.2017.23.1.085</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>교신저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr"/>
     </row>
@@ -3865,37 +3861,37 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Assessing Sensitivity of Paddy Rice to Climate Change in South Korea</t>
+          <t>Analysis of the characteristics of the global virtual water trade network using degree and eigenvector centrality, with a focus on food and feed crops</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Soo-Jin Kim, Seung-Jong Bae, Sorae Kim, Seung‐Hwan Yoo, Min-Won Jang</t>
+          <t>Sang‐Hyun Lee, Rabi H. Mohtar, Jin‐Yong Choi, Seung‐Hwan Yoo</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Hydrology and earth system sciences</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>554-554</t>
+          <t>4223-4235</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>10.3390/w8120554</t>
+          <t>10.5194/hess-20-4223-2016</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -3905,11 +3901,11 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>교신저자</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="M63" s="2" t="inlineStr"/>
     </row>
@@ -3922,37 +3918,37 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Effects of climate change on paddy water use efficiency with temporal change in the transplanting and growing season in South Korea</t>
+          <t>Assessing Sensitivity of Paddy Rice to Climate Change in South Korea</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Sang‐Hyun Lee, Seung‐Hwan Yoo, Jin‐Yong Choi, Bernard A. Engel</t>
+          <t>Soo-Jin Kim, Seung-Jong Bae, Sorae Kim, Seung‐Hwan Yoo, Min-Won Jang</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Irrigation Science</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>443-463</t>
+          <t>554</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>10.1007/s00271-016-0514-8</t>
+          <t>10.3390/w8120554</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -3962,11 +3958,11 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>교신저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="M64" s="2" t="inlineStr"/>
     </row>
@@ -3979,37 +3975,37 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Estimation of pollutant unit load of paddy fields with and without a rainfall factor</t>
+          <t>Effects of climate change on paddy water use efficiency with temporal change in the transplanting and growing season in South Korea</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Dongho Choi, Kwang‐Sik Yoon, Woo‐Jung Choi, Seung‐Hwan Yoo</t>
+          <t>Sang‐Hyun Lee, Seung‐Hwan Yoo, Jin‐Yong Choi, Bernard A. Engel</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Irrigation and Drainage</t>
+          <t>Irrigation Science</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>112-120</t>
+          <t>443-463</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>10.1002/ird.2027</t>
+          <t>10.1007/s00271-016-0514-8</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -4019,11 +4015,11 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>교신저자</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="M65" s="2" t="inlineStr"/>
     </row>
@@ -4036,37 +4032,37 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Evaluation of external virtual water export and dependency through crop trade: an Asian case study</t>
+          <t>Estimation of pollutant unit load of paddy fields with and without a rainfall factor</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Sang‐Hyun Lee, Seung‐Hwan Yoo, Jin‐Yong Choi, Rabi H. Mohtar</t>
+          <t>Dongho Choi, Kwang‐Sik Yoon, Woo‐Jung Choi, Seung‐Hwan Yoo</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Paddy and Water Environment</t>
+          <t>Irrigation and Drainage</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>65</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>525-539</t>
+          <t>112-120</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>10.1007/s10333-016-0569-4</t>
+          <t>10.1002/ird.2027</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -4076,11 +4072,11 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>교신저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M66" s="2" t="inlineStr"/>
     </row>
@@ -4183,7 +4179,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -4238,7 +4234,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -4338,7 +4334,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -4495,7 +4491,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -4550,7 +4546,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -4605,7 +4601,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -4660,7 +4656,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -4760,7 +4756,7 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4782,37 +4778,37 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>MONITORING OF SHALLOW GROUNDWATER SALINITY IN LIVESTOCK MANURE APPLICATIONS TO RECLAIMED TIDAL LAND</t>
+          <t>Estimating water footprint of paddy rice in Korea</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Eun Mi Hong, Jin‐Yong Choi, Seung‐Hwan Yoo, Won‐Ho Nam</t>
+          <t>Seung-Hwan Yoo, Jin-Yong Choi, Sang Hyun Lee, Tae‐Gon Kim</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Irrigation and Drainage</t>
+          <t>Paddy and Water Environment</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>63-74</t>
+          <t>43-54</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>10.1002/ird.1787</t>
+          <t>10.1007/s10333-013-0358-2</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -4822,11 +4818,11 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>주저자</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="M80" s="2" t="inlineStr"/>
     </row>
@@ -4839,40 +4835,42 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>RCP 시나리오 기반 농업용 저수지의 내한능력 평가</t>
+          <t>MONITORING OF SHALLOW GROUNDWATER SALINITY IN LIVESTOCK MANURE APPLICATIONS TO RECLAIMED TIDAL LAND</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>박나영, 최진용, 유승환, 이상현</t>
+          <t>Eun Mi Hong, Jin‐Yong Choi, Seung‐Hwan Yoo, Won‐Ho Nam</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="n">
-        <v>55</v>
+          <t>Irrigation and Drainage</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>13-24</t>
+          <t>63-74</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2013.55.3.013</t>
+          <t>10.1002/ird.1787</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -4894,42 +4892,40 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Regional Drought Assessment Considering Climate Change and Relationship with Agricultural Water in Jeju Island</t>
+          <t>RCP 시나리오 기반 농업용 저수지의 내한능력 평가</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Sung‐Ho Song, Seung‐Hwan Yoo, Seung-Jong Bae</t>
+          <t>박나영, 최진용, 유승환, 이상현</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Journal of Environmental Science International</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>55</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>625-638</t>
+          <t>13-24</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>10.5322/jesi.2013.22.5.625</t>
+          <t>10.5389/KSAE.2013.55.3.013</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -4938,7 +4934,7 @@
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M82" s="2" t="inlineStr"/>
     </row>
@@ -4951,40 +4947,42 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>둑높이기 농업용저수지의 운영기준에 따른 환경용수 방류패턴 분석</t>
+          <t>Regional Drought Assessment Considering Climate Change and Relationship with Agricultural Water in Jeju Island</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>이상현, 유승환, 박나영, 최진용</t>
+          <t>Sung‐Ho Song, Seung‐Hwan Yoo, Seung-Jong Bae</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="n">
-        <v>55</v>
+          <t>Journal of Environmental Science International</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>51-62</t>
+          <t>625-638</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2013.55.3.051</t>
+          <t>10.5322/jesi.2013.22.5.625</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>국내 기타</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4993,7 +4991,7 @@
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M83" s="2" t="inlineStr"/>
     </row>
@@ -5006,12 +5004,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>수문인자추출에서의 SRTM DEM (Shuttle Radar Topography Mission Digital Elevation Model) 적용성 평가: 대동강 및 금강 지역 사례연구</t>
+          <t>둑높이기 농업용저수지의 운영기준에 따른 환경용수 방류패턴 분석</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>허용구, 유승환</t>
+          <t>이상현, 유승환, 박나영, 최진용</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -5024,31 +5022,31 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>101-112</t>
+          <t>51-62</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2013.55.6.101</t>
+          <t>10.5389/KSAE.2013.55.3.051</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>교신저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M84" s="2" t="inlineStr"/>
     </row>
@@ -5061,39 +5059,49 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>저소득층 노후주택 단열성능 개선(희망의 방한칸프로젝트)을 통한 효과 분석</t>
+          <t>수문인자추출에서의 SRTM DEM (Shuttle Radar Topography Mission Digital Elevation Model) 적용성 평가: 대동강 및 금강 지역 사례연구</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>김정화, 유승환, Jong Hoon Kim, 정학근, 장성호, 장철용</t>
+          <t>허용구, 유승환</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>대한설비공학회 2013년도 하계학술발표대회</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" s="2" t="inlineStr"/>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>725-728</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr"/>
+          <t>101-112</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>10.5389/KSAE.2013.55.6.101</t>
+        </is>
+      </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>교신저자</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" s="2" t="inlineStr"/>
     </row>
@@ -5102,46 +5110,34 @@
         <v>85</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>A decision support system for agricultural drought management using risk assessment</t>
+          <t>저소득층 노후주택 단열성능 개선(희망의 방한칸프로젝트)을 통한 효과 분석</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Won‐Ho Nam, Jin‐Yong Choi, Seung‐Hwan Yoo, Min-Won Jang</t>
+          <t>김정화, 유승환, Jong Hoon Kim, 정학근, 장성호, 장철용</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Paddy and Water Environment</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>대한설비공학회 2013년도 하계학술발표대회</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>197-207</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>10.1007/s10333-012-0329-z</t>
-        </is>
-      </c>
+          <t>725-728</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>국내 기타</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -5150,7 +5146,7 @@
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr"/>
     </row>
@@ -5163,22 +5159,22 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>A real-time online drought broadcast system for monitoring soil moisture index</t>
+          <t>A decision support system for agricultural drought management using risk assessment</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Won‐Ho Nam, Jin‐Yong Choi, Seung‐Hwan Yoo, Bernard A. Engel</t>
+          <t>Won‐Ho Nam, Jin‐Yong Choi, Seung‐Hwan Yoo, Min-Won Jang</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>KSCE Journal of Civil Engineering</t>
+          <t>Paddy and Water Environment</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -5188,17 +5184,17 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>357-365</t>
+          <t>197-207</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>10.1007/s12205-012-1357-3</t>
+          <t>10.1007/s10333-012-0329-z</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -5207,7 +5203,7 @@
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="M87" s="2" t="inlineStr"/>
     </row>
@@ -5220,47 +5216,51 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Analysis of design water requirement of paddy rice using frequency analysis affected by climate change in South Korea</t>
+          <t>A real-time online drought broadcast system for monitoring soil moisture index</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Seung‐Hwan Yoo, Jin‐Yong Choi, Won‐Ho Nam, Eunmi Hong</t>
+          <t>Won‐Ho Nam, Jin‐Yong Choi, Seung‐Hwan Yoo, Bernard A. Engel</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Agricultural Water Management</t>
+          <t>KSCE Journal of Civil Engineering</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr"/>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>33-42</t>
+          <t>357-365</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.agwat.2012.06.002</t>
+          <t>10.1007/s12205-012-1357-3</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>국내 기타</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>주저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M88" s="2" t="inlineStr"/>
     </row>
@@ -5273,12 +5273,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Climate change impacts on water storage requirements of an agricultural reservoir considering changes in land use and rice growing season in Korea</t>
+          <t>Analysis of design water requirement of paddy rice using frequency analysis affected by climate change in South Korea</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Yoo Seung-Hwan, Jin‐Yong Choi, Sang‐Hyun Lee, Yun‐Gyeong Oh, Yun Dong Koun</t>
+          <t>Seung‐Hwan Yoo, Jin‐Yong Choi, Won‐Ho Nam, Eunmi Hong</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -5288,18 +5288,18 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>112</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>43-54</t>
+          <t>33-42</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.agwat.2012.10.023</t>
+          <t>10.1016/j.agwat.2012.06.002</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -5313,7 +5313,7 @@
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="M89" s="2" t="inlineStr"/>
     </row>
@@ -5326,38 +5326,38 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Estimation of Agricultural Water and Land Required to Substitute the Import of Feed-grain for Domestic Production</t>
+          <t>Climate change impacts on water storage requirements of an agricultural reservoir considering changes in land use and rice growing season in Korea</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Seung‐Hwan Yoo, Jeongbin Im, Jin Yong Choi, Sanghyun Lee</t>
+          <t>Yoo Seung-Hwan, Jin‐Yong Choi, Sang‐Hyun Lee, Yun‐Gyeong Oh, Yun Dong Koun</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Journal of the Korean Society of International Agriculture</t>
+          <t>Agricultural Water Management</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>259-264</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr"/>
+          <t>43-54</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>10.1016/j.agwat.2012.10.023</t>
+        </is>
+      </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="M90" s="2" t="inlineStr"/>
     </row>
@@ -5379,47 +5379,47 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Evaluating spatial centrality for integrated tourism management in rural areas using GIS and network analysis</t>
+          <t>Estimation of Agricultural Water and Land Required to Substitute the Import of Feed-grain for Domestic Production</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Sang-Hyun Lee, Jin‐Yong Choi, Seung-Hwan Yoo, Yun‐Gyeong Oh</t>
+          <t>Seung‐Hwan Yoo, Jeongbin Im, Jin Yong Choi, Sanghyun Lee</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Tourism Management</t>
+          <t>Journal of the Korean Society of International Agriculture</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr"/>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>14-24</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.tourman.2012.03.005</t>
-        </is>
-      </c>
+          <t>259-264</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>국내 기타</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>주저자</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>145</v>
+        <v>3</v>
       </c>
       <c r="M91" s="2" t="inlineStr"/>
     </row>
@@ -5432,30 +5432,38 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>가로주택정비사업 대상지 선정을 위한 서울시 공간구조 분석</t>
+          <t>Evaluating spatial centrality for integrated tourism management in rural areas using GIS and network analysis</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>임재성, 박현신, 유승환, 강준모</t>
+          <t>Sang-Hyun Lee, Jin‐Yong Choi, Seung-Hwan Yoo, Yun‐Gyeong Oh</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>한국도시설계학회 추계학술발표대회 논문집</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr"/>
+          <t>Tourism Management</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>192-199</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr"/>
+          <t>14-24</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>10.1016/j.tourman.2012.03.005</t>
+        </is>
+      </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -5464,7 +5472,7 @@
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="M92" s="2" t="inlineStr"/>
     </row>
@@ -5477,49 +5485,39 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>고해상도 기후시나리오를 이용한 논용수 수요량 및 단위용수량의 기후변화 영향 분석</t>
+          <t>가로주택정비사업 대상지 선정을 위한 서울시 공간구조 분석</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>유승환, 최진용, 이상현, 오윤경, 박나영</t>
+          <t>임재성, 박현신, 유승환, 강준모</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>한국도시설계학회 추계학술발표대회 논문집</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>15-26</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>10.5389/KSAE.2012.54.2.015</t>
-        </is>
-      </c>
+          <t>192-199</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr"/>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>국내 기타</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>주저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr"/>
     </row>
@@ -5532,12 +5530,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>기후변화 시나리오 (A1B)에 따른 농업용 저수지 유역의 미래 토지피복변화 예측 및 논 면적 변화 특성 분석</t>
+          <t>고해상도 기후시나리오를 이용한 논용수 수요량 및 단위용수량의 기후변화 영향 분석</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>오윤경, 유승환, 이상현, 박나영, 최진용, 윤동균</t>
+          <t>유승환, 최진용, 이상현, 오윤경, 박나영</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -5555,26 +5553,26 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>77-86</t>
+          <t>15-26</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2012.54.2.077</t>
+          <t>10.5389/KSAE.2012.54.2.015</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>주저자</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="M94" s="2" t="inlineStr"/>
     </row>
@@ -5587,12 +5585,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>기후변화 시나리오에 따른 미래 논벼의 소비수량 및 생산량 변화 분석</t>
+          <t>기후변화 시나리오 (A1B)에 따른 농업용 저수지 유역의 미래 토지피복변화 예측 및 논 면적 변화 특성 분석</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>이태석, 최진용, 유승환, 이상현, 오윤경</t>
+          <t>오윤경, 유승환, 이상현, 박나영, 최진용, 윤동균</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -5605,22 +5603,22 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>47-54</t>
+          <t>77-86</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2012.54.1.047</t>
+          <t>10.5389/KSAE.2012.54.2.077</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -5629,7 +5627,7 @@
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="M95" s="2" t="inlineStr"/>
     </row>
@@ -5642,38 +5640,40 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>기후변화의 농업환경 요인 영향을 고려한 미래 농어촌용수 수요 평가</t>
+          <t>기후변화 시나리오에 따른 미래 논벼의 소비수량 및 생산량 변화 분석</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Jin-Yong Choi, 유승환, Yun Kyung Oh, 이상현, 윤동균</t>
+          <t>이태석, 최진용, 유승환, 이상현, 오윤경</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>물과 미래 : 한국수자원학회지 = Water for future</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>54</v>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>73-83</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr"/>
+          <t>47-54</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>10.5389/KSAE.2012.54.1.047</t>
+        </is>
+      </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M96" s="2" t="inlineStr"/>
     </row>
@@ -5695,21 +5695,23 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>농업가뭄대응을 위한 가뭄기상시나리오 모델 개발 및 적용</t>
+          <t>기후변화의 농업환경 요인 영향을 고려한 미래 농어촌용수 수요 평가</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>유승환, 최진용, 남원호, 김태곤, 고광돈</t>
+          <t>Jin-Yong Choi, 유승환, Yun Kyung Oh, 이상현, 윤동균</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="n">
-        <v>54</v>
+          <t>물과 미래 : 한국수자원학회지 = Water for future</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
@@ -5718,26 +5720,22 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>67-75</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>10.5389/KSAE.2012.54.2.067</t>
-        </is>
-      </c>
+          <t>73-83</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr"/>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>국내 기타</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>주저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr"/>
     </row>
@@ -5750,12 +5748,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>둑높이기 농업용저수지의 환경용수 방류기준 설정</t>
+          <t>농업가뭄대응을 위한 가뭄기상시나리오 모델 개발 및 적용</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>유승환, 이상현, 최진용, 박태선</t>
+          <t>유승환, 최진용, 남원호, 김태곤, 고광돈</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -5768,22 +5766,22 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>17-24</t>
+          <t>67-75</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2012.54.5.017</t>
+          <t>10.5389/KSAE.2012.54.2.067</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -5792,7 +5790,7 @@
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M98" s="2" t="inlineStr"/>
     </row>
@@ -5805,39 +5803,49 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>소형임대주택 공급을 위한 대상지 선정에 관한 기초연구</t>
+          <t>둑높이기 농업용저수지의 환경용수 방류기준 설정</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>진형석, 박현신, 유승환, 강준모</t>
+          <t>유승환, 이상현, 최진용, 박태선</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>한국도시설계학회 추계학술발표대회 논문집</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr"/>
-      <c r="G99" s="2" t="inlineStr"/>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>260-268</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr"/>
+          <t>17-24</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>10.5389/KSAE.2012.54.5.017</t>
+        </is>
+      </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>주저자</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M99" s="2" t="inlineStr"/>
     </row>
@@ -5850,40 +5858,30 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>잣나무림에서의 시기별 토층별 토양수분 특성분석</t>
+          <t>소형임대주택 공급을 위한 대상지 선정에 관한 기초연구</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>홍은미, 최진용, 유승환, 남원호</t>
+          <t>진형석, 박현신, 유승환, 강준모</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>한국도시설계학회 추계학술발표대회 논문집</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>105-114</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>10.5389/KSAE.2012.54.4.105</t>
-        </is>
-      </c>
+          <t>260-268</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr"/>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>국내 기타</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -5892,7 +5890,7 @@
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M100" s="2" t="inlineStr"/>
     </row>
@@ -5901,55 +5899,53 @@
         <v>100</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Estimation of the international virtual water flow of grain crop products in Korea</t>
+          <t>잣나무림에서의 시기별 토층별 토양수분 특성분석</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Seung-Hwan Yoo, Tae‐Gon Kim, Jeong-Bin Im, Jin-Yong Choi</t>
+          <t>홍은미, 최진용, 유승환, 남원호</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Paddy and Water Environment</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>54</v>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>83-93</t>
+          <t>105-114</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>10.1007/s10333-011-0267-1</t>
+          <t>10.5389/KSAE.2012.54.4.105</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>주저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M101" s="2" t="inlineStr"/>
     </row>
@@ -5962,49 +5958,51 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>기후변화 시나리오에 따른 미래 토지피복변화 예측 및 군집분석을 이용한 지역 특성 분석</t>
+          <t>Estimation of the international virtual water flow of grain crop products in Korea</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>오윤경, 최진용, 유승환, 이상현</t>
+          <t>Seung-Hwan Yoo, Tae‐Gon Kim, Jeong-Bin Im, Jin-Yong Choi</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="n">
-        <v>53</v>
+          <t>Paddy and Water Environment</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>31-41</t>
+          <t>83-93</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2011.53.6.031</t>
+          <t>10.1007/s10333-011-0267-1</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>주저자</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M102" s="2" t="inlineStr"/>
     </row>
@@ -6017,12 +6015,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>침엽수 산림에서의 토양수분 감쇄특성 분석</t>
+          <t>기후변화 시나리오에 따른 미래 토지피복변화 예측 및 군집분석을 이용한 지역 특성 분석</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>홍은미, 최진용, 남원호, 유승환</t>
+          <t>오윤경, 최진용, 유승환, 이상현</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -6035,22 +6033,22 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>1-9</t>
+          <t>31-41</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2011.53.4.001</t>
+          <t>10.5389/KSAE.2011.53.6.031</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -6059,7 +6057,7 @@
         </is>
       </c>
       <c r="L103" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M103" s="2" t="inlineStr"/>
     </row>
@@ -6068,42 +6066,44 @@
         <v>103</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>A Probability Mapping for Land Cover Change Prediction using CLUE Model</t>
+          <t>침엽수 산림에서의 토양수분 감쇄특성 분석</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Yun‐Gyeong Oh, Jin‐Yong Choi, Seung-Jong Bae, Seung‐Hwan Yoo, Sang Hyun Lee</t>
+          <t>홍은미, 최진용, 남원호, 유승환</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Journal of Korean Society of Rural Planning</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>53</v>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>47-55</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr"/>
+          <t>1-9</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>10.5389/KSAE.2011.53.4.001</t>
+        </is>
+      </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M104" s="2" t="inlineStr"/>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       <c r="I108" s="2" t="inlineStr"/>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>435504-435504</t>
+          <t>435504</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -7210,7 +7210,7 @@
       <c r="G125" s="2" t="inlineStr"/>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>301-301</t>
+          <t>301</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr"/>

--- a/files/me-ADPER0000095429.xlsx
+++ b/files/me-ADPER0000095429.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M127"/>
+  <dimension ref="A1:M125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -626,52 +626,48 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Analysis of Application of Design Standards for Future Climate Change Adaptive Agricultural Reservoirs Using Cluster Analysis</t>
+          <t>Development and utilization of agricultural and rural climate information systems to respond to climate crisis</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Dong-Hyuk Joo, 라 나, Hayoung Kim, Seung-Hwan Yoo, Sang-Hyun Lee</t>
+          <t>Hayoung Kim, 나라, Dong-Hyuk Joo, Euigeon So, Seung-Hwan Yoo, Seung-Jong Bae, Soo-Jin Kim, Yeong-cheol Kwak, ByeongWoo Choi, K. Park, DalJu Park, YunPyo Lee, MyungWon Lee, YongDuk Shin</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Water</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+          <t>한국기후변화학회지</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>16</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3463</t>
+          <t>1129-1139</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10.3390/w17243463</t>
+          <t>10.15531/ksccr.2025.16.5.1129</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>교신저자</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>1</v>
-      </c>
+          <t>공저자</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
@@ -683,35 +679,35 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Development and utilization of agricultural and rural climate information systems to respond to climate crisis</t>
+          <t>공동체부문 농업환경보전프로그램 대상지 선정기준 개선 및 중요도 조사</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Hayoung Kim, 나라, Dong-Hyuk Joo, Euigeon So, Seung-Hwan Yoo, Seung-Jong Bae, Soo-Jin Kim, Yeong-cheol Kwak, ByeongWoo Choi, K. Park, DalJu Park, YunPyo Lee, MyungWon Lee, YongDuk Shin</t>
+          <t>배승종, 김수진, 유승환</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>한국기후변화학회지</t>
+          <t>농촌계획</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1129-1139</t>
+          <t>225-231</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10.15531/ksccr.2025.16.5.1129</t>
+          <t>10.7851/ksrp.2025.31.4.225</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -724,7 +720,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
@@ -736,12 +734,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>공동체부문 농업환경보전프로그램 대상지 선정기준 개선 및 중요도 조사</t>
+          <t>농업·농촌 정보체계의 활용도와 접근성에 관한 실증적 분석 - 사업 실무자 설문조사를 중심으로 -</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>배승종, 김수진, 유승환</t>
+          <t>리재웅, 이상현, 유승환, 김진성, 김동중, 취뤼, 이향미</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -759,12 +757,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>225-231</t>
+          <t>29-42</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2025.31.4.225</t>
+          <t>10.7851/ksrp.2025.31.4.029</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -791,35 +789,35 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>농업·농촌 정보체계의 활용도와 접근성에 관한 실증적 분석 - 사업 실무자 설문조사를 중심으로 -</t>
+          <t>농업용 저수지의 가능최대홍수량 설계를 위한 하류부 피해 산정 방안 적용성 분석</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>리재웅, 이상현, 유승환, 김진성, 김동중, 취뤼, 이향미</t>
+          <t>주동혁, 나라, 김하영, 소의건, 송인홍, 이성학, 신길채, 심규현, 허건, 유승환</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
+          <t>한국농공학회논문집</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29-42</t>
+          <t>59-70</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2025.31.4.029</t>
+          <t>10.5389/KSAE.2025.67.3.059</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -832,9 +830,7 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L7" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
@@ -846,12 +842,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>농업용 저수지의 가능최대홍수량 설계를 위한 하류부 피해 산정 방안 적용성 분석</t>
+          <t>농업용 저수지의 홍수기 운영을 위한 상당강우-저류용량-관리수위 곡선 적용성 분석</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>주동혁, 나라, 김하영, 소의건, 송인홍, 이성학, 신길채, 심규현, 허건, 유승환</t>
+          <t>신길채, 나라, 주동혁, 박상빈, 유승환</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -864,17 +860,17 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59-70</t>
+          <t>35-49</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2025.67.3.059</t>
+          <t>10.5389/KSAE.2025.67.4.035</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -899,21 +895,21 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>농업용 저수지의 홍수기 운영을 위한 상당강우-저류용량-관리수위 곡선 적용성 분석</t>
+          <t>농업환경보전프로그램 이행점검을 위한 시스템 설계</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>신길채, 나라, 주동혁, 박상빈, 유승환</t>
+          <t>나라, 주동혁, 유승환, 배승종, 박호철, 최규훈, 성재훈, 최진용, 손정우, 허승오</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
+          <t>농촌계획</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -922,12 +918,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35-49</t>
+          <t>55-67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2025.67.4.035</t>
+          <t>10.7851/ksrp.2025.31.4.055</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -940,7 +936,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
@@ -952,12 +950,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>농업환경보전프로그램 이행점검을 위한 시스템 설계</t>
+          <t>농업환경보전프로그램의 농업환경 영향평가를 위한 시스템 개발</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>나라, 주동혁, 유승환, 배승종, 박호철, 최규훈, 성재훈, 최진용, 손정우, 허승오</t>
+          <t>손정우, 허승오, 유승환</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -975,12 +973,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55-67</t>
+          <t>215-224</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2025.31.4.055</t>
+          <t>10.7851/ksrp.2025.31.4.215</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1003,39 +1001,39 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>농업환경보전프로그램의 농업환경 영향평가를 위한 시스템 개발</t>
+          <t>Development of a future weather database based on Shared Socioeconomic Pathways scenarios for assessing climate change vulnerability of agricultural infrastructure</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>손정우, 허승오, 유승환</t>
+          <t>Dong-Hyuk Joo, 나라, Ha-Young Kim, Jaepil Cho, JuHyoung Lee, Suk-ho Song, DalJu Park, , YunPyo Lee, MyoungWon Lee, Seung-Hwan Yoo</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
+          <t>한국기후변화학회지</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>215-224</t>
+          <t>953-964</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2025.31.4.215</t>
+          <t>10.15531/ksccr.2024.15.5.953</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1048,9 +1046,7 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L11" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1062,48 +1058,52 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Development of a future weather database based on Shared Socioeconomic Pathways scenarios for assessing climate change vulnerability of agricultural infrastructure</t>
+          <t>The Application of a Smart Nexus for Agriculture in Korea for Assessing the Holistic Impacts of Climate Change</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Dong-Hyuk Joo, 나라, Ha-Young Kim, Jaepil Cho, JuHyoung Lee, Suk-ho Song, DalJu Park, , YunPyo Lee, MyoungWon Lee, Seung-Hwan Yoo</t>
+          <t>라 나, Seung‐Hwan Yoo, Sang‐Hyun Lee, Jin‐Yong Choi, Seung-Oh Hur, Pu Reun Yoon, Kwang Soo Kim</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>한국기후변화학회지</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>15</v>
+          <t>Sustainability</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>953-964</t>
+          <t>990</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10.15531/ksccr.2024.15.5.953</t>
+          <t>10.3390/su16030990</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>수집 학회지</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
+          <t>교신저자</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="M12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1111,56 +1111,52 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>The Application of a Smart Nexus for Agriculture in Korea for Assessing the Holistic Impacts of Climate Change</t>
+          <t>K-HAS와 비율보정 계수를 이용한 농업용 저수지의 비상연계 용수공급 가능량 분석</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>라 나, Seung‐Hwan Yoo, Sang‐Hyun Lee, Jin‐Yong Choi, Seung-Oh Hur, Pu Reun Yoon, Kwang Soo Kim</t>
+          <t>김하영, 이상현, 나라, 주동혁, 유승환</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Sustainability</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>65</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>59-71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10.3390/su16030990</t>
+          <t>10.5389/KSAE.2023.65.2.059</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>교신저자</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>8</v>
-      </c>
+          <t>공저자</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1172,48 +1168,48 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>K-HAS와 비율보정 계수를 이용한 농업용 저수지의 비상연계 용수공급 가능량 분석</t>
+          <t>Transboundary water-food nexus based on physical-virtual water embedded in food trade network</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>김하영, 이상현, 나라, 주동혁, 유승환</t>
+          <t>Sang‐Hyun Lee, Makoto Taniguchi, Naoki Masuhara, Seung‐Hwan Yoo, Yun‐Gyeong Oh, Masahiko Haraguchi, Rui Qu</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Journal of Hydrology</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59-71</t>
+          <t>129819</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2023.65.2.059</t>
+          <t>10.1016/j.jhydrol.2023.129819</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>수집 학회지</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
+          <t>교신저자</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="M14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1225,48 +1221,48 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Transboundary water-food nexus based on physical-virtual water embedded in food trade network</t>
+          <t>농업용 수로부의 수위 보정을 위한 필터기법별 적용성 분석</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Sang‐Hyun Lee, Makoto Taniguchi, Naoki Masuhara, Seung‐Hwan Yoo, Yun‐Gyeong Oh, Masahiko Haraguchi, Rui Qu</t>
+          <t>주동혁, 나라, 김하영, 최규훈, 윤형창, 박상빈, 유승환</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Journal of Hydrology</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>623</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>129819</t>
+          <t>51-68</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.jhydrol.2023.129819</t>
+          <t>10.5389/KSAE.2023.65.5.051</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>교신저자</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>9</v>
-      </c>
+          <t>공저자</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1278,12 +1274,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>농업용 수로부의 수위 보정을 위한 필터기법별 적용성 분석</t>
+          <t>농업용 저수지의 하한 관리 저수율 설정에 따른 농업용수 및 환경용수 공급 가능성 고찰</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>주동혁, 나라, 김하영, 최규훈, 윤형창, 박상빈, 유승환</t>
+          <t>정지연, 정민혁, 범진아, 박민경, 이재남, 유승환, 윤광식</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1296,17 +1292,17 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51-68</t>
+          <t>21-33</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2023.65.5.051</t>
+          <t>10.5389/KSAE.2023.65.2.021</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1331,35 +1327,35 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>농업용 저수지의 하한 관리 저수율 설정에 따른 농업용수 및 환경용수 공급 가능성 고찰</t>
+          <t>농업환경보전프로그램 이행단계별 문제점 및 애로사항에 대한 이해당사자별 인식 비교</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>정지연, 정민혁, 범진아, 박민경, 이재남, 유승환, 윤광식</t>
+          <t>김수진, 배승종, 유승환, 나라, 손정우, 허승오</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
+          <t>농촌계획</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21-33</t>
+          <t>201-210</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2023.65.2.021</t>
+          <t>10.7851/ksrp.2023.29.4.201</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1372,7 +1368,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="M17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1384,35 +1382,35 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>농업환경보전프로그램 이행단계별 문제점 및 애로사항에 대한 이해당사자별 인식 비교</t>
+          <t>딥러닝 기법을 이용한 농업용저수지 CCTV 영상 기반의 수위계측 방법 개발</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>김수진, 배승종, 유승환, 나라, 손정우, 허승오</t>
+          <t>주동혁, 이상현, 최규훈, 유승환, 나라, 김하영, 오창조, 윤광식</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
+          <t>한국농공학회논문집</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>201-210</t>
+          <t>15-26</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2023.29.4.201</t>
+          <t>10.5389/KSAE.2023.65.1.015</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1425,9 +1423,7 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L18" s="2" t="n">
-        <v>2</v>
-      </c>
+      <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1439,21 +1435,21 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>딥러닝 기법을 이용한 농업용저수지 CCTV 영상 기반의 수위계측 방법 개발</t>
+          <t>물-에너지-식량-탄소 넥서스를 이용한 통합물관리 모델 평가 연구 - 영산강 수계를 중심으로 -</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>주동혁, 이상현, 최규훈, 유승환, 나라, 김하영, 오창조, 윤광식</t>
+          <t>나라, 박진현, 주동혁, 김하영, 유승환, 오창조, 이상현, 오부영, 허승오</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
+          <t>농촌계획</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
@@ -1462,12 +1458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15-26</t>
+          <t>37-49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2023.65.1.015</t>
+          <t>10.7851/ksrp.2023.29.1.037</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1480,7 +1476,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1488,44 +1486,42 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>물-에너지-식량-탄소 넥서스를 이용한 통합물관리 모델 평가 연구 - 영산강 수계를 중심으로 -</t>
+          <t>Analysis of climate change impact on resource intensity and carbon emissions in protected farming systems using Water-Energy-Food-Carbon Nexus</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>나라, 박진현, 주동혁, 김하영, 유승환, 오창조, 이상현, 오부영, 허승오</t>
+          <t>Pu Reun Yoon, Sang‐Hyun Lee, Jin‐Yong Choi, Seung‐Hwan Yoo, Seung-Oh Hur</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Resources Conservation and Recycling</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37-49</t>
+          <t>106394</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2023.29.1.037</t>
+          <t>10.1016/j.resconrec.2022.106394</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>수집 학회지</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1534,7 +1530,7 @@
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M20" s="2" t="inlineStr"/>
     </row>
@@ -1547,33 +1543,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Analysis of climate change impact on resource intensity and carbon emissions in protected farming systems using Water-Energy-Food-Carbon Nexus</t>
+          <t>Development of WEF-P Nexus based on product-supply chain: A case study of phosphorous fertilizer industry in Morocco</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Pu Reun Yoon, Sang‐Hyun Lee, Jin‐Yong Choi, Seung‐Hwan Yoo, Seung-Oh Hur</t>
+          <t>Sang‐Hyun Lee, Amjad T. Assi, Rabi H. Mohtar, Meryem Hamane, Pu Reun Yoon, Seung‐Hwan Yoo</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Resources Conservation and Recycling</t>
+          <t>The Science of The Total Environment</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Pt 2</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>106394</t>
+          <t>159520</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.resconrec.2022.106394</t>
+          <t>10.1016/j.scitotenv.2022.159520</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1583,11 +1583,11 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>교신저자</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
     </row>
@@ -1600,51 +1600,49 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Development of WEF-P Nexus based on product-supply chain: A case study of phosphorous fertilizer industry in Morocco</t>
+          <t>농업경영체 등록정보와 공간정보를 활용한 농지범용화 사업 대상지 선정 방안 개발 및 적용</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Sang‐Hyun Lee, Amjad T. Assi, Rabi H. Mohtar, Meryem Hamane, Pu Reun Yoon, Seung‐Hwan Yoo</t>
+          <t>나라, 주동혁, 김하영, 유승환, 곽영철, 김정훈, 이향미, 조은정</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>The Science of The Total Environment</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>857</t>
-        </is>
+          <t>농촌계획</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>28</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Pt 2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>159520</t>
+          <t>17-26</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.scitotenv.2022.159520</t>
+          <t>10.7851/ksrp.2022.28.1.017</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>교신저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr"/>
     </row>
@@ -1657,35 +1655,35 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>농업경영체 등록정보와 공간정보를 활용한 농지범용화 사업 대상지 선정 방안 개발 및 적용</t>
+          <t>농업용저수지의 실시간 수위 보정을 위한 Hampel Filter의 최적 Window Size 분석</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>나라, 주동혁, 김하영, 유승환, 곽영철, 김정훈, 이향미, 조은정</t>
+          <t>주동혁, 나라, 김하영, 최규훈, 권재환, 유승환</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
+          <t>한국농공학회논문집</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17-26</t>
+          <t>9-24</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2022.28.1.017</t>
+          <t>10.5389/KSAE.2022.64.3.009</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1698,9 +1696,7 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L23" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1712,12 +1708,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>농업용저수지의 실시간 수위 보정을 위한 Hampel Filter의 최적 Window Size 분석</t>
+          <t>설계강우의 지속시간 및 시간분포에 따른 배수개선 농경지 침수 영향 분석</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>주동혁, 나라, 김하영, 최규훈, 권재환, 유승환</t>
+          <t>전상민, 김귀훈, 이현지, 강기호, 유승환, 최진용, 강문성</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1730,17 +1726,17 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9-24</t>
+          <t>47-55</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2022.64.3.009</t>
+          <t>10.5389/KSAE.2022.64.2.047</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1761,52 +1757,52 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>설계강우의 지속시간 및 시간분포에 따른 배수개선 농경지 침수 영향 분석</t>
+          <t>Analysis of industrial water–energy–labor nexus zones for economic and resource-based impact assessment</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>전상민, 김귀훈, 이현지, 강기호, 유승환, 최진용, 강문성</t>
+          <t>Sang‐Hyun Lee, Makoto Taniguchi, Naoki Masuhara, Rabi H. Mohtar, Seung‐Hwan Yoo, Masahiko Haraguchi</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Resources Conservation and Recycling</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>47-55</t>
+          <t>105483</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2022.64.2.047</t>
+          <t>10.1016/j.resconrec.2021.105483</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>수집 학회지</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr"/>
+          <t>교신저자</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>19</v>
+      </c>
       <c r="M25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1818,33 +1814,37 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Analysis of industrial water–energy–labor nexus zones for economic and resource-based impact assessment</t>
+          <t>Assessing the Potential of Agricultural Reservoirs as the Source of Environmental Flow</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Sang‐Hyun Lee, Makoto Taniguchi, Naoki Masuhara, Rabi H. Mohtar, Seung‐Hwan Yoo, Masahiko Haraguchi</t>
+          <t>Young-Jun Jo, Jung‐Hun Song, Younggu Her, Giorgio Provolo, Jina Beom, Minhyuk Jeung, Young‐Joo Kim, Seung‐Hwan Yoo, Kwang‐Sik Yoon</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Resources Conservation and Recycling</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>105483</t>
+          <t>508</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.resconrec.2021.105483</t>
+          <t>10.3390/w13040508</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -1854,11 +1854,11 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>교신저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="M26" s="2" t="inlineStr"/>
     </row>
@@ -1871,42 +1871,42 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Assessing the Potential of Agricultural Reservoirs as the Source of Environmental Flow</t>
+          <t>Evaluation of Irrigation Safety by Operation Management of Water Supply from Large Scale Agricultural Reservoirs</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Young-Jun Jo, Jung‐Hun Song, Younggu Her, Giorgio Provolo, Jina Beom, Minhyuk Jeung, Young‐Joo Kim, Seung‐Hwan Yoo, Kwang‐Sik Yoon</t>
+          <t>Minhyuk Jeung, Jina Beom, Mu-hong Sung, Jaenam Lee, Seung‐Hwan Yoo, Kwang-sik Yoon</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Korean Society of Hazard Mitigation</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>189-198</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10.3390/w13040508</t>
+          <t>10.9798/kosham.2021.21.1.189</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>국내 기타</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M27" s="2" t="inlineStr"/>
     </row>
@@ -1928,42 +1928,38 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Evaluation of Irrigation Safety by Operation Management of Water Supply from Large Scale Agricultural Reservoirs</t>
+          <t>Vulnerability assessment of rural aging community for abandoned farmlands in South Korea</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Minhyuk Jeung, Jina Beom, Mu-hong Sung, Jaenam Lee, Seung‐Hwan Yoo, Kwang-sik Yoon</t>
+          <t>Jimin Lee, Yun‐Gyeong Oh, Seung‐Hwan Yoo, Kyo Suh</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Korean Society of Hazard Mitigation</t>
+          <t>Land Use Policy</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>189-198</t>
+          <t>105544</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10.9798/kosham.2021.21.1.189</t>
+          <t>10.1016/j.landusepol.2021.105544</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1972,7 +1968,7 @@
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="M28" s="2" t="inlineStr"/>
     </row>
@@ -1985,38 +1981,40 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Vulnerability assessment of rural aging community for abandoned farmlands in South Korea</t>
+          <t>농업생산기반정비사업의 예비타당성조사 정책효과 분석 - 판교지구 다목적 농촌용수개발사업을 중심으로 -</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Jimin Lee, Yun‐Gyeong Oh, Seung‐Hwan Yoo, Kyo Suh</t>
+          <t>김수진, 배승종, 유승환, 김윤형, 윤성은, 김정훈</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Land Use Policy</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr"/>
+          <t>농촌계획</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>105544</t>
+          <t>21-28</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.landusepol.2021.105544</t>
+          <t>10.7851/ksrp.2021.27.1.021</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2025,7 +2023,7 @@
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr"/>
     </row>
@@ -2038,35 +2036,35 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>농업생산기반정비사업의 예비타당성조사 정책효과 분석 - 판교지구 다목적 농촌용수개발사업을 중심으로 -</t>
+          <t>농업용 저수지의 농업가뭄에 대한 기후변화 잠재영향 평가</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>김수진, 배승종, 유승환, 김윤형, 윤성은, 김정훈</t>
+          <t>김수진, 황세운, 배승종, 유승환, 최진용, 장민원</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
+          <t>한국농공학회논문집</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21-28</t>
+          <t>141-150</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2021.27.1.021</t>
+          <t>10.5389/KSAE.2021.63.6.141</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2079,9 +2077,7 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L30" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
@@ -2093,12 +2089,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>농업용 저수지의 농업가뭄에 대한 기후변화 잠재영향 평가</t>
+          <t>대규모 농업용저수지 수혜면적 변화에 따른 효율적 용수재분배 모의</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>김수진, 황세운, 배승종, 유승환, 최진용, 장민원</t>
+          <t>성무홍, 정민혁, 범진아, 박태선, 이재남, 정형모, 김영주, 유승환, 윤광식</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2111,17 +2107,17 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>141-150</t>
+          <t>1-12</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2021.63.6.141</t>
+          <t>10.5389/KSAE.2021.63.3.001</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2134,7 +2130,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
@@ -2146,12 +2144,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>대규모 농업용저수지 수혜면적 변화에 따른 효율적 용수재분배 모의</t>
+          <t>수리·수문설계시스템 및 비율보정계수 기법을 활용한 농업용 저수지의 홍수기 운영기준 평가</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>성무홍, 정민혁, 범진아, 박태선, 이재남, 정형모, 김영주, 유승환, 윤광식</t>
+          <t>정형모, 이상현, 김경환, 곽영철, 최은혁, 윤성은, 나라, 주동혁, 유승환, 윤광식</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2164,17 +2162,17 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1-12</t>
+          <t>97-104</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2021.63.3.001</t>
+          <t>10.5389/KSAE.2021.63.4.097</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2188,7 +2186,7 @@
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M32" s="2" t="inlineStr"/>
     </row>
@@ -2201,12 +2199,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>수리·수문설계시스템 및 비율보정계수 기법을 활용한 농업용 저수지의 홍수기 운영기준 평가</t>
+          <t>필터링 기법을 이용한 농업용저수지 수위자료의 품질관리 방안</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>정형모, 이상현, 김경환, 곽영철, 최은혁, 윤성은, 나라, 주동혁, 유승환, 윤광식</t>
+          <t>김경환, 최규훈, 정형모, 주동혁, 나라, 최은혁, 권재환, 유승환</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2219,17 +2217,17 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>97-104</t>
+          <t>83-93</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2021.63.4.097</t>
+          <t>10.5389/KSAE.2021.63.5.083</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2242,9 +2240,7 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L33" s="2" t="n">
-        <v>2</v>
-      </c>
+      <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
@@ -2252,52 +2248,56 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>필터링 기법을 이용한 농업용저수지 수위자료의 품질관리 방안</t>
+          <t>A Proposal of Start-up Education Program for Designer</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>김경환, 최규훈, 정형모, 주동혁, 나라, 최은혁, 권재환, 유승환</t>
+          <t>Seung Hwan Yoo, Bo Hyeon Yoo</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>63</v>
+          <t>Journal of Cultural Product &amp; Design</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>83-93</t>
+          <t>73-82</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2021.63.5.083</t>
+          <t>10.18555/kicpd.2020.63.07</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>수집 학회지</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr"/>
+          <t>주저자</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
@@ -2309,37 +2309,37 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>A Proposal of Start-up Education Program for Designer</t>
+          <t>Assessing the Resilience of Agricultural Reservoirs in Ungauged Catchments under Climate Change Using a Ratio Correction Factors-Based Calibration and Run Theory</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Seung Hwan Yoo, Bo Hyeon Yoo</t>
+          <t>Sang‐Hyun Lee, Sungtae Shin, Jin‐Yong Choi, Jihoon Park, Seung‐Hwan Yoo</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Journal of Cultural Product &amp; Design</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>73-82</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10.18555/kicpd.2020.63.07</t>
+          <t>10.3390/w12061618</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2349,11 +2349,11 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>주저자</t>
+          <t>교신저자</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M35" s="2" t="inlineStr"/>
     </row>
@@ -2366,12 +2366,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Assessing the Resilience of Agricultural Reservoirs in Ungauged Catchments under Climate Change Using a Ratio Correction Factors-Based Calibration and Run Theory</t>
+          <t>Evaluating the Impact of Climate Change on Paddy Water Balance Using APEX-Paddy Model</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Sang‐Hyun Lee, Sungtae Shin, Jin‐Yong Choi, Jihoon Park, Seung‐Hwan Yoo</t>
+          <t>Mohammad Kamruzzaman, Syewoon Hwang, Soon-Kun Choi, Jaepil Cho, Inhong Song, Jung‐Hun Song, Hanseok Jeong, Taeil Jang, Seung‐Hwan Yoo</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2386,17 +2386,17 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>852</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>10.3390/w12061618</t>
+          <t>10.3390/w12030852</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2406,11 +2406,11 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>교신저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
     </row>
@@ -2423,37 +2423,33 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Evaluating the Impact of Climate Change on Paddy Water Balance Using APEX-Paddy Model</t>
+          <t>Food-centric interlinkages in agricultural food-energy-water nexus under climate change and irrigation management</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Mohammad Kamruzzaman, Syewoon Hwang, Soon-Kun Choi, Jaepil Cho, Inhong Song, Jung‐Hun Song, Hanseok Jeong, Taeil Jang, Seung‐Hwan Yoo</t>
+          <t>Sang‐Hyun Lee, Jin‐Yong Choi, Seung-Oh Hur, Makoto Taniguchi, Naoki Masuhara, Kwang Soo Kim, Shinwoo Hyun, Eunhee Choi, Jae-hoon Sung, Seung‐Hwan Yoo</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Resources Conservation and Recycling</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>105099</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10.3390/w12030852</t>
+          <t>10.1016/j.resconrec.2020.105099</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2463,11 +2459,11 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>교신저자</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="M37" s="2" t="inlineStr"/>
     </row>
@@ -2480,33 +2476,33 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Food-centric interlinkages in agricultural food-energy-water nexus under climate change and irrigation management</t>
+          <t>Prediction of the effects of management practices on discharge and mineral nitrogen yield from paddy fields under future climate using APEX-paddy model</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Sang‐Hyun Lee, Jin‐Yong Choi, Seung-Oh Hur, Makoto Taniguchi, Naoki Masuhara, Kwang Soo Kim, Shinwoo Hyun, Eunhee Choi, Jae-hoon Sung, Seung‐Hwan Yoo</t>
+          <t>Mohammad Kamruzzaman, Syewoon Hwang, Soon-Kun Choi, Jaepil Cho, Inhong Song, Hanseok Jeong, Jung‐Hun Song, Teail Jang, Seung‐Hwan Yoo</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Resources Conservation and Recycling</t>
+          <t>Agricultural Water Management</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>105099</t>
+          <t>106345</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.resconrec.2020.105099</t>
+          <t>10.1016/j.agwat.2020.106345</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2516,11 +2512,11 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>교신저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="M38" s="2" t="inlineStr"/>
     </row>
@@ -2533,38 +2529,40 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Prediction of the effects of management practices on discharge and mineral nitrogen yield from paddy fields under future climate using APEX-paddy model</t>
+          <t>가뭄 대응형 지하수 개발 우선순위 선정을 위한 농촌용수구역의 유형 분석</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Mohammad Kamruzzaman, Syewoon Hwang, Soon-Kun Choi, Jaepil Cho, Inhong Song, Hanseok Jeong, Jung‐Hun Song, Teail Jang, Seung‐Hwan Yoo</t>
+          <t>오윤경, 이상현, 김아라, 홍순욱, 유승환</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Agricultural Water Management</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr"/>
+          <t>농촌계획</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>106345</t>
+          <t>51-59</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.agwat.2020.106345</t>
+          <t>10.7851/Ksrp.2020.26.2.051</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2573,7 +2571,7 @@
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr"/>
     </row>
@@ -2586,12 +2584,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>가뭄 대응형 지하수 개발 우선순위 선정을 위한 농촌용수구역의 유형 분석</t>
+          <t>기후변화에 따른 농업생산기반시설 영향분석을 통한 정책추진 방안 연구</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>오윤경, 이상현, 김아라, 홍순욱, 유승환</t>
+          <t>정경훈, 송석호, 정형모, 오승헌, 김수진, 임세윤, 주동혁, 황세운, 장민원, 배승종, 유승환</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2604,17 +2602,17 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>51-59</t>
+          <t>81-91</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>10.7851/Ksrp.2020.26.2.051</t>
+          <t>10.7851/ksrp.2020.26.4.081</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2628,7 +2626,7 @@
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M40" s="2" t="inlineStr"/>
     </row>
@@ -2641,35 +2639,35 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>기후변화에 따른 농업생산기반시설 영향분석을 통한 정책추진 방안 연구</t>
+          <t>미래 수요예측을 통한 제주도 농업용수 회복탄력적 공급 방안에 관한 연구</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>정경훈, 송석호, 정형모, 오승헌, 김수진, 임세윤, 주동혁, 황세운, 장민원, 배승종, 유승환</t>
+          <t>고재한, 정민혁, 범진아, 성무홍, 정형모, 유승환, 윤광식</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
+          <t>한국농공학회논문집</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>81-91</t>
+          <t>71-83</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2020.26.4.081</t>
+          <t>10.5389/KSAE.2020.62.3.071</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2682,9 +2680,7 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L41" s="2" t="n">
-        <v>3</v>
-      </c>
+      <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
@@ -2696,40 +2692,38 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>미래 수요예측을 통한 제주도 농업용수 회복탄력적 공급 방안에 관한 연구</t>
+          <t>한국조사연구학회 발표 논문 내용분석, 1999∼2019년: 학문분야ㆍ방법론ㆍ연구대상ㆍ데이터분석기법의 지속과 변동</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>고재한, 정민혁, 범진아, 성무홍, 정형모, 유승환, 윤광식</t>
+          <t>Dong-Hoon Seol, 고재훈, 유승환, 이기재</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>62</v>
+          <t>조사연구</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>71-83</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>10.5389/KSAE.2020.62.3.071</t>
-        </is>
-      </c>
+          <t>1-32</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>수집 학회지</t>
+          <t>국내 기타</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2737,7 +2731,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
@@ -2745,26 +2741,26 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>한국조사연구학회 발표 논문 내용분석, 1999∼2019년: 학문분야ㆍ방법론ㆍ연구대상ㆍ데이터분석기법의 지속과 변동</t>
+          <t>Assessment of food trade impacts on water, food, and land security in the MENA region</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Dong-Hoon Seol, 고재훈, 유승환, 이기재</t>
+          <t>Sang‐Hyun Lee, Rabi H. Mohtar, Seung‐Hwan Yoo</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>조사연구</t>
+          <t>Hydrology and earth system sciences</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -2774,22 +2770,26 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1-32</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
+          <t>557-572</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>10.5194/hess-23-557-2019</t>
+        </is>
+      </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>교신저자</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M43" s="2" t="inlineStr"/>
     </row>
@@ -2802,22 +2802,22 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Assessment of food trade impacts on water, food, and land security in the MENA region</t>
+          <t>Uncertainty in hydrological analysis of climate change: multi-parameter vs. multi-GCM ensemble predictions</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Sang‐Hyun Lee, Rabi H. Mohtar, Seung‐Hwan Yoo</t>
+          <t>Younggu Her, Seung‐Hwan Yoo, Jaepil Cho, Syewoon Hwang, Jaehak Jeong, Chounghyun Seong</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Hydrology and earth system sciences</t>
+          <t>Scientific Reports</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>557-572</t>
+          <t>4974</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>10.5194/hess-23-557-2019</t>
+          <t>10.1038/s41598-019-41334-7</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>56</v>
+        <v>288</v>
       </c>
       <c r="M44" s="2" t="inlineStr"/>
     </row>
@@ -2859,51 +2859,49 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Uncertainty in hydrological analysis of climate change: multi-parameter vs. multi-GCM ensemble predictions</t>
+          <t>기후변화 대응을 위한 양수장의 농업가뭄 취약성 실태 평가</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Younggu Her, Seung‐Hwan Yoo, Jaepil Cho, Syewoon Hwang, Jaehak Jeong, Chounghyun Seong</t>
+          <t>장민원, 김수진, 배승종, 유승환, 정경훈, 황세운</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Scientific Reports</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>61</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>4974</t>
+          <t>31-40</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>10.1038/s41598-019-41334-7</t>
+          <t>10.5389/KSAE.2019.61.6.031</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>교신저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>286</v>
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr"/>
     </row>
@@ -2916,12 +2914,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>기후변화 대응을 위한 양수장의 농업가뭄 취약성 실태 평가</t>
+          <t>농업용저수지를 이용한 환경생태유량 확보방안 경제성 비교 연구 - 동복천을 중심으로 -</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>장민원, 김수진, 배승종, 유승환, 정경훈, 황세운</t>
+          <t>박진현, 고재한, 성무홍, 정형모, 박태선, 곽영철, 최우영, 범진아, 정민혁, 유승환, 윤광식</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2934,17 +2932,17 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>31-40</t>
+          <t>33-47</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2019.61.6.031</t>
+          <t>10.5389/KSAE.2019.61.5.033</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -2957,9 +2955,7 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L46" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
@@ -2967,52 +2963,56 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>농업용저수지를 이용한 환경생태유량 확보방안 경제성 비교 연구 - 동복천을 중심으로 -</t>
+          <t>An Analysis of the Water-Energy-Food-Land Requirements and CO2 Emissions for Food Security of Rice in Japan</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>박진현, 고재한, 성무홍, 정형모, 박태선, 곽영철, 최우영, 범진아, 정민혁, 유승환, 윤광식</t>
+          <t>Sang‐Hyun Lee, Makoto Taniguchi, Rabi H. Mohtar, Jin‐Yong Choi, Seung‐Hwan Yoo</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>61</v>
+          <t>Sustainability</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>33-47</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2019.61.5.033</t>
+          <t>10.3390/su10093354</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>수집 학회지</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr"/>
+          <t>교신저자</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>32</v>
+      </c>
       <c r="M47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
@@ -3024,17 +3024,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>An Analysis of the Water-Energy-Food-Land Requirements and CO2 Emissions for Food Security of Rice in Japan</t>
+          <t>Analysis of Drought Intensity and Trends Using the Modified SPEI in South Korea from 1981 to 2010</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Sang‐Hyun Lee, Makoto Taniguchi, Rabi H. Mohtar, Jin‐Yong Choi, Seung‐Hwan Yoo</t>
+          <t>Seung-Jong Bae, Sang-Hyun Lee, Seung-Hwan Yoo, Tae‐Gon Kim</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Sustainability</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>327</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>10.3390/su10093354</t>
+          <t>10.3390/w10030327</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -3064,11 +3064,11 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>교신저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="M48" s="2" t="inlineStr"/>
     </row>
@@ -3081,37 +3081,37 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Analysis of Drought Intensity and Trends Using the Modified SPEI in South Korea from 1981 to 2010</t>
+          <t>Water footprint for Korean rice products and virtual water trade in a water-energy-food nexus</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Seung-Jong Bae, Sang Hyun Lee, Seung-Hwan Yoo, Tae‐Gon Kim</t>
+          <t>Sang‐Hyun Lee, Jin‐Yong Choi, Seung‐Hwan Yoo, Rabi H. Mohtar</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Water International</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>871-886</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>10.3390/w10030327</t>
+          <t>10.1080/02508060.2018.1515570</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="M49" s="2" t="inlineStr"/>
     </row>
@@ -3138,42 +3138,40 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Water footprint for Korean rice products and virtual water trade in a water-energy-food nexus</t>
+          <t>농어촌용수 및 농업생산기반시설의 실태조사에 따른 기후변화 영향 분석</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Sang‐Hyun Lee, Jin‐Yong Choi, Seung‐Hwan Yoo, Rabi H. Mohtar</t>
+          <t>김수진, 배승종, 최진용, 김성필, 은상규, 유승환, 장태일, 고남영, 황세운, 김성준, 박태선, 정경훈, 송석호</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Water International</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>60</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>871-886</t>
+          <t>1-15</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>10.1080/02508060.2018.1515570</t>
+          <t>10.5389/KSAE.2018.60.5.001</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -3182,7 +3180,7 @@
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr"/>
     </row>
@@ -3195,12 +3193,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>농어촌용수 및 농업생산기반시설의 실태조사에 따른 기후변화 영향 분석</t>
+          <t>농업경영체 등록정보를 활용한 밭 경작지의 공간적 파편화 특성 분석</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>김수진, 배승종, 최진용, 김성필, 은상규, 유승환, 장태일, 고남영, 황세운, 김성준, 박태선, 정경훈, 송석호</t>
+          <t>이지민, 유승환, 오윤경</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3213,17 +3211,17 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>1-15</t>
+          <t>13-24</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2018.60.5.001</t>
+          <t>10.5389/KSAE.2018.60.2.013</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -3236,9 +3234,7 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
@@ -3250,12 +3246,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>농업경영체 등록정보를 활용한 밭 경작지의 공간적 파편화 특성 분석</t>
+          <t>농업경영체 등록정보와 공간데이터를 활용한 밭 이용 방안 연구: 전라남도 무안군·해남군을 중심으로</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>이지민, 유승환, 오윤경</t>
+          <t>오윤경, 유승환, 최수명, 이지민</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3268,17 +3264,17 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>13-24</t>
+          <t>27-35</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2018.60.2.013</t>
+          <t>10.5389/KSAE.2018.60.4.027</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3291,7 +3287,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
@@ -3303,12 +3301,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>농업경영체 등록정보와 공간데이터를 활용한 밭 이용 방안 연구: 전라남도 무안군·해남군을 중심으로</t>
+          <t>물-에너지-식량-토지 넥서스를 통한 미래 쌀 수급 변화에 따른 자원별 이용량 변화 분석</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>오윤경, 유승환, 최수명, 이지민</t>
+          <t>이상현, 최진용, 유승환, 허승오</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3326,12 +3324,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>27-35</t>
+          <t>93-103</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2018.60.4.027</t>
+          <t>10.5389/KSAE.2018.60.4.093</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3345,7 +3343,7 @@
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="2" t="inlineStr"/>
     </row>
@@ -3358,12 +3356,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>물-에너지-식량-토지 넥서스를 통한 미래 쌀 수급 변화에 따른 자원별 이용량 변화 분석</t>
+          <t>지형 특성과 경작지 분포를 고려한 밭정비 유형 분석 - 무안군과 화순군 비교 -</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>이상현, 최진용, 유승환, 허승오</t>
+          <t>이지민, 유승환, 오윤경, 김아라</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3376,17 +3374,17 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>93-103</t>
+          <t>133-144</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2018.60.4.093</t>
+          <t>10.5389/KSAE.2018.60.6.133</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -3399,9 +3397,7 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L54" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
@@ -3413,12 +3409,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>지형 특성과 경작지 분포를 고려한 밭정비 유형 분석 - 무안군과 화순군 비교 -</t>
+          <t>회복탄력성을 고려한 기상 시나리오별 가뭄 용수 공급방안: 나주호를 중심으로</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>이지민, 유승환, 오윤경, 김아라</t>
+          <t>박진현, 고재한, 조영준, 정경훈, 성무홍, 정형모, 박현규, 유승환, 윤광식</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3431,17 +3427,17 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>133-144</t>
+          <t>115-124</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2018.60.6.133</t>
+          <t>10.5389/KSAE.2018.60.5.115</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3454,7 +3450,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="M55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
@@ -3462,53 +3460,55 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>회복탄력성을 고려한 기상 시나리오별 가뭄 용수 공급방안: 나주호를 중심으로</t>
+          <t>Assessment of the Impact of Climate Change on Drought Characteristics in the Hwanghae Plain, North Korea Using Time Series SPI and SPEI: 1981–2100</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>박진현, 고재한, 조영준, 정경훈, 성무홍, 정형모, 박현규, 유승환, 윤광식</t>
+          <t>Sanghyun Lee, Seung‐Hwan Yoo, Jin‐Yong Choi, Seung-Jong Bae</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="n">
-        <v>60</v>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>115-124</t>
+          <t>579</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2018.60.5.115</t>
+          <t>10.3390/w9080579</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>수집 학회지</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>교신저자</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>110</v>
       </c>
       <c r="M56" s="2" t="inlineStr"/>
     </row>
@@ -3521,37 +3521,37 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Assessment of the Impact of Climate Change on Drought Characteristics in the Hwanghae Plain, North Korea Using Time Series SPI and SPEI: 1981–2100</t>
+          <t>Extension of Typical Meteorological Data and Energy Demand Analysis for Building Energy Efficiency Rating Certification System</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Sanghyun Lee, Seung‐Hwan Yoo, Jin‐Yong Choi, Seung-Jong Bae</t>
+          <t>Sung Lee, Jonghun Kim, Hakgeun Jeong, Seung‐Hwan Yoo, Jung Hun Lee</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>KIEAE Journal</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>13-20</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>10.3390/w9080579</t>
+          <t>10.12813/kieae.2017.17.2.013</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3561,11 +3561,11 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>교신저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr"/>
     </row>
@@ -3578,37 +3578,37 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Extension of Typical Meteorological Data and Energy Demand Analysis for Building Energy Efficiency Rating Certification System</t>
+          <t>GCM‐related uncertainty in forecasting irrigation and design water requirement for paddy rice fields</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Sung Lee, Jonghun Kim, Hakgeun Jeong, Seung‐Hwan Yoo, Jung Hun Lee</t>
+          <t>Sang‐Hyun Lee, 승환 유, Jin‐Yong Choi, Syewoon Hwang</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>KIEAE Journal</t>
+          <t>International Journal of Climatology</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>38</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>13-20</t>
+          <t>1298-1313</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>10.12813/kieae.2017.17.2.013</t>
+          <t>10.1002/joc.5244</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -3618,11 +3618,11 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>교신저자</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M58" s="2" t="inlineStr"/>
     </row>
@@ -3635,22 +3635,22 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>GCM‐related uncertainty in forecasting irrigation and design water requirement for paddy rice fields</t>
+          <t>Nonparametric quantile mapping using the response surface method – bias correction of daily precipitation</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Sang‐Hyun Lee, 승환 유, Jin‐Yong Choi, Syewoon Hwang</t>
+          <t>Taeho Bong, Younghwan Son, Seung‐Hwan Yoo, Syewoon Hwang</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>International Journal of Climatology</t>
+          <t>Journal of Water and Climate Change</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>1298-1313</t>
+          <t>525-539</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>10.1002/joc.5244</t>
+          <t>10.2166/wcc.2017.127</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -3675,11 +3675,11 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>교신저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M59" s="2" t="inlineStr"/>
     </row>
@@ -3692,42 +3692,40 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Nonparametric quantile mapping using the response surface method – bias correction of daily precipitation</t>
+          <t>경제성 지표를 활용한 농업용저수지의 생활용수 공급가능성 평가</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Taeho Bong, Younghwan Son, Seung‐Hwan Yoo, Syewoon Hwang</t>
+          <t>윤광식, 최수명, 채종훈, 유승환, 최동호, 윤석군, 이창희, 정경훈, 신길채</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Journal of Water and Climate Change</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>농촌계획</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>23</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>525-539</t>
+          <t>85-96</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>10.2166/wcc.2017.127</t>
+          <t>10.7851/ksrp.2017.23.1.085</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3736,7 +3734,7 @@
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr"/>
     </row>
@@ -3745,55 +3743,55 @@
         <v>60</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>The effect of plasma on shear bond strength between resin cement and colored zirconia</t>
+          <t>Analysis of the characteristics of the global virtual water trade network using degree and eigenvector centrality, with a focus on food and feed crops</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Chan Park, Seung-Hwan Yoo, Sang-Won Park, Kwi‐Dug Yun, Min-Kyung Ji, Jin-Ho Shin, Hyun‐Pil Lim</t>
+          <t>Sang‐Hyun Lee, Rabi H. Mohtar, Jin‐Yong Choi, Seung‐Hwan Yoo</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>The Journal of Advanced Prosthodontics</t>
+          <t>Hydrology and earth system sciences</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>4223-4235</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>10.4047/jap.2017.9.2.118</t>
+          <t>10.5194/hess-20-4223-2016</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>교신저자</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="M61" s="2" t="inlineStr"/>
     </row>
@@ -3802,44 +3800,46 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>경제성 지표를 활용한 농업용저수지의 생활용수 공급가능성 평가</t>
+          <t>Assessing Sensitivity of Paddy Rice to Climate Change in South Korea</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>윤광식, 최수명, 채종훈, 유승환, 최동호, 윤석군, 이창희, 정경훈, 신길채</t>
+          <t>Soo-Jin Kim, Seung-Jong Bae, Sorae Kim, Seung‐Hwan Yoo, Min-Won Jang</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="n">
-        <v>23</v>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>85-96</t>
+          <t>554</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2017.23.1.085</t>
+          <t>10.3390/w8120554</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>수집 학회지</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M62" s="2" t="inlineStr"/>
     </row>
@@ -3861,37 +3861,37 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Analysis of the characteristics of the global virtual water trade network using degree and eigenvector centrality, with a focus on food and feed crops</t>
+          <t>Effects of climate change on paddy water use efficiency with temporal change in the transplanting and growing season in South Korea</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Sang‐Hyun Lee, Rabi H. Mohtar, Jin‐Yong Choi, Seung‐Hwan Yoo</t>
+          <t>Sang‐Hyun Lee, Seung‐Hwan Yoo, Jin‐Yong Choi, Bernard A. Engel</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Hydrology and earth system sciences</t>
+          <t>Irrigation Science</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>4223-4235</t>
+          <t>443-463</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>10.5194/hess-20-4223-2016</t>
+          <t>10.1007/s00271-016-0514-8</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M63" s="2" t="inlineStr"/>
     </row>
@@ -3918,37 +3918,37 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Assessing Sensitivity of Paddy Rice to Climate Change in South Korea</t>
+          <t>Estimation of pollutant unit load of paddy fields with and without a rainfall factor</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Soo-Jin Kim, Seung-Jong Bae, Sorae Kim, Seung‐Hwan Yoo, Min-Won Jang</t>
+          <t>Dongho Choi, Kwang‐Sik Yoon, Woo‐Jung Choi, Seung‐Hwan Yoo</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Irrigation and Drainage</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>65</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>112-120</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>10.3390/w8120554</t>
+          <t>10.1002/ird.2027</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M64" s="2" t="inlineStr"/>
     </row>
@@ -3975,37 +3975,37 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Effects of climate change on paddy water use efficiency with temporal change in the transplanting and growing season in South Korea</t>
+          <t>Evaluation of external virtual water export and dependency through crop trade: an Asian case study</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Sang‐Hyun Lee, Seung‐Hwan Yoo, Jin‐Yong Choi, Bernard A. Engel</t>
+          <t>Sang‐Hyun Lee, Seung‐Hwan Yoo, Jin‐Yong Choi, Rabi H. Mohtar</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Irrigation Science</t>
+          <t>Paddy and Water Environment</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>443-463</t>
+          <t>525-539</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>10.1007/s00271-016-0514-8</t>
+          <t>10.1007/s10333-016-0569-4</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="M65" s="2" t="inlineStr"/>
     </row>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Estimation of pollutant unit load of paddy fields with and without a rainfall factor</t>
+          <t>Evaluation of the Dependency and Intensity of the Virtual Water Trade in Korea</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Dongho Choi, Kwang‐Sik Yoon, Woo‐Jung Choi, Seung‐Hwan Yoo</t>
+          <t>Sang‐Hyun Lee, Seung‐Hwan Yoo, Jin‐Yong Choi, Ankook Shin</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -4052,17 +4052,17 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>112-120</t>
+          <t>48-56</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>10.1002/ird.2027</t>
+          <t>10.1002/ird.1957</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -4072,11 +4072,11 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>교신저자</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M66" s="2" t="inlineStr"/>
     </row>
@@ -4089,51 +4089,49 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Evaluation of the Dependency and Intensity of the Virtual Water Trade in Korea</t>
+          <t>기후변화 시나리오를 이용한 미래 읍면동단위 기준증발산량 데이터베이스 설계 및 구축</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Sang‐Hyun Lee, Seung‐Hwan Yoo, Jin‐Yong Choi, Ankook Shin</t>
+          <t>김태곤, 서교, 남원호, 이제명, 황세운, 유승환, 홍순욱</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Irrigation and Drainage</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
+          <t>농촌계획</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>22</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>48-56</t>
+          <t>71-80</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>10.1002/ird.1957</t>
+          <t>10.7851/ksrp.2016.22.4.071</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>교신저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M67" s="2" t="inlineStr"/>
     </row>
@@ -4146,35 +4144,35 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>기후변화 시나리오를 이용한 미래 읍면동단위 기준증발산량 데이터베이스 설계 및 구축</t>
+          <t>쌀 생산 및 소비에 따른 지역 간 청색 가상수 흐름 추정을 통한 지역 수자원의 기여도 분석</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>김태곤, 서교, 남원호, 이제명, 황세운, 유승환, 홍순욱</t>
+          <t>이상현, 최진용, 유승환, 김윤형</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
+          <t>한국농공학회논문집</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>71-80</t>
+          <t>73-80</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2016.22.4.071</t>
+          <t>10.5389/KSAE.2016.58.1.073</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -4188,7 +4186,7 @@
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr"/>
     </row>
@@ -4201,40 +4199,30 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>쌀 생산 및 소비에 따른 지역 간 청색 가상수 흐름 추정을 통한 지역 수자원의 기여도 분석</t>
+          <t>저소득층 가구 표준모델을 이용한 저소득층 에너지효율개선사업의 에너지 및 온실가스 절감 효과 분석</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>이상현, 최진용, 유승환, 김윤형</t>
+          <t>김정국, 장철용, 유승환, 정학근, 송두삼, 이정훈, Jong Hoon Kim</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>대한설비공학회 2016년도 하계학술발표대회</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>73-80</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>10.5389/KSAE.2016.58.1.073</t>
-        </is>
-      </c>
+          <t>284-287</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>수집 학회지</t>
+          <t>국내 기타</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -4256,30 +4244,40 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>저소득층 가구 표준모델을 이용한 저소득층 에너지효율개선사업의 에너지 및 온실가스 절감 효과 분석</t>
+          <t>적용 기법에 따른 강우침식인자 산정 결과의 시공간적 불확실성</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>김정국, 장철용, 유승환, 정학근, 송두삼, 이정훈, Jong Hoon Kim</t>
+          <t>황세운, 김동현, 신상민, 유승환</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>대한설비공학회 2016년도 하계학술발표대회</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr"/>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>284-287</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr"/>
+          <t>55-69</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>10.5389/KSAE.2016.58.6.055</t>
+        </is>
+      </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -4288,7 +4286,7 @@
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr"/>
     </row>
@@ -4301,49 +4299,39 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>적용 기법에 따른 강우침식인자 산정 결과의 시공간적 불확실성</t>
+          <t>토픽 모델링을 활용한 초등 도덕 교과서 내용 분석</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>황세운, 김동현, 신상민, 유승환</t>
+          <t>유승환</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>한국사회학회 사회학대회 논문집</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>55-69</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>10.5389/KSAE.2016.58.6.055</t>
-        </is>
-      </c>
+          <t>703-717</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>수집 학회지</t>
+          <t>국내 기타</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>주저자·교신</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr"/>
     </row>
@@ -4352,43 +4340,55 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>토픽 모델링을 활용한 초등 도덕 교과서 내용 분석</t>
+          <t>Estimation of potential water requirements using water footprint for the target of food self-sufficiency in South Korea</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>유승환</t>
+          <t>Seung‐Hwan Yoo, Sang‐Hyun Lee, Jin‐Yong Choi, Jeongbin Im</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>한국사회학회 사회학대회 논문집</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" s="2" t="inlineStr"/>
+          <t>Paddy and Water Environment</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>703-717</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr"/>
+          <t>259-269</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>10.1007/s10333-015-0495-x</t>
+        </is>
+      </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>주저자·교신</t>
+          <t>주저자</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M72" s="2" t="inlineStr"/>
     </row>
@@ -4401,42 +4401,40 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Estimation of potential water requirements using water footprint for the target of food self-sufficiency in South Korea</t>
+          <t>농업수자원 기후변화 영향평가를 위한 CMIP5 GCMs의 기후 전망자료 경향성 분석</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Seung‐Hwan Yoo, Sang‐Hyun Lee, Jin‐Yong Choi, Jeongbin Im</t>
+          <t>유승환, 김태곤, 이상현, 최진용</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Paddy and Water Environment</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>57</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>259-269</t>
+          <t>69-80</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>10.1007/s10333-015-0495-x</t>
+          <t>10.5389/KSAE.2015.57.5.069</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -4445,7 +4443,7 @@
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="M73" s="2" t="inlineStr"/>
     </row>
@@ -4458,12 +4456,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>농업수자원 기후변화 영향평가를 위한 CMIP5 GCMs의 기후 전망자료 경향성 분석</t>
+          <t>식품 소비 및 칼로리 공급 변화에 따른 가상수 소비량의 변화 분석</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>유승환, 김태곤, 이상현, 최진용</t>
+          <t>이상현, 최진용, 유승환</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -4476,17 +4474,17 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>69-80</t>
+          <t>77-86</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2015.57.5.069</t>
+          <t>10.5389/KSAE.2015.57.3.077</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -4496,11 +4494,11 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>주저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M74" s="2" t="inlineStr"/>
     </row>
@@ -4513,12 +4511,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>식품 소비 및 칼로리 공급 변화에 따른 가상수 소비량의 변화 분석</t>
+          <t>액비 시비에 따른 포플러시험포 토양수 및 천층지하수 수질 영향 평가</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>이상현, 최진용, 유승환</t>
+          <t>홍은미, 최진용, 남원호, 이상현, 유승환</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -4531,17 +4529,17 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>77-86</t>
+          <t>25-35</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2015.57.3.077</t>
+          <t>10.5389/KSAE.2015.57.1.025</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -4555,7 +4553,7 @@
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr"/>
     </row>
@@ -4568,12 +4566,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>액비 시비에 따른 포플러시험포 토양수 및 천층지하수 수질 영향 평가</t>
+          <t>한국의 축산물 물발자국 산정</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>홍은미, 최진용, 남원호, 이상현, 유승환</t>
+          <t>이상현, 최진용, 유승환, 김영득, 신안국</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4586,17 +4584,17 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>25-35</t>
+          <t>85-92</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2015.57.1.025</t>
+          <t>10.5389/KSAE.2015.57.2.085</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -4610,7 +4608,7 @@
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M76" s="2" t="inlineStr"/>
     </row>
@@ -4619,44 +4617,34 @@
         <v>76</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>한국의 축산물 물발자국 산정</t>
+          <t>Push To Talk을 이용한 스마트폰 화물 배차 시스템</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>이상현, 최진용, 유승환, 김영득, 신안국</t>
+          <t>김동현, 박주한, 유승환, 한상필</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>한국정보과학회 학술발표논문집</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>85-92</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>10.5389/KSAE.2015.57.2.085</t>
-        </is>
-      </c>
+          <t>1299-1301</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>수집 학회지</t>
+          <t>국내 기타</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -4665,7 +4653,7 @@
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr"/>
     </row>
@@ -4678,39 +4666,49 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Push To Talk을 이용한 스마트폰 화물 배차 시스템</t>
+          <t>한국의 밭작물 생산에서의 물발자국 산정</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>김동현, 박주한, 유승환, 한상필</t>
+          <t>유승환, 이상현, 최진용</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>한국정보과학회 학술발표논문집</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr"/>
-      <c r="G78" s="2" t="inlineStr"/>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>1299-1301</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr"/>
+          <t>65-74</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>10.5389/KSAE.2014.56.3.065</t>
+        </is>
+      </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>주저자</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M78" s="2" t="inlineStr"/>
     </row>
@@ -4719,44 +4717,46 @@
         <v>78</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>한국의 밭작물 생산에서의 물발자국 산정</t>
+          <t>Estimating water footprint of paddy rice in Korea</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>유승환, 이상현, 최진용</t>
+          <t>Seung-Hwan Yoo, Jin-Yong Choi, Sang-Hyun Lee, Tae‐Gon Kim</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="n">
-        <v>56</v>
+          <t>Paddy and Water Environment</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>65-74</t>
+          <t>43-54</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2014.56.3.065</t>
+          <t>10.1007/s10333-013-0358-2</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>수집 학회지</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="M79" s="2" t="inlineStr"/>
     </row>
@@ -4778,37 +4778,37 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Estimating water footprint of paddy rice in Korea</t>
+          <t>MONITORING OF SHALLOW GROUNDWATER SALINITY IN LIVESTOCK MANURE APPLICATIONS TO RECLAIMED TIDAL LAND</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Seung-Hwan Yoo, Jin-Yong Choi, Sang Hyun Lee, Tae‐Gon Kim</t>
+          <t>Eun Mi Hong, Jin‐Yong Choi, Seung‐Hwan Yoo, Won‐Ho Nam</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Paddy and Water Environment</t>
+          <t>Irrigation and Drainage</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>62</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>43-54</t>
+          <t>63-74</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>10.1007/s10333-013-0358-2</t>
+          <t>10.1002/ird.1787</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -4818,11 +4818,11 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>주저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="M80" s="2" t="inlineStr"/>
     </row>
@@ -4835,42 +4835,40 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>MONITORING OF SHALLOW GROUNDWATER SALINITY IN LIVESTOCK MANURE APPLICATIONS TO RECLAIMED TIDAL LAND</t>
+          <t>RCP 시나리오 기반 농업용 저수지의 내한능력 평가</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Eun Mi Hong, Jin‐Yong Choi, Seung‐Hwan Yoo, Won‐Ho Nam</t>
+          <t>박나영, 최진용, 유승환, 이상현</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Irrigation and Drainage</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>55</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>63-74</t>
+          <t>13-24</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>10.1002/ird.1787</t>
+          <t>10.5389/KSAE.2013.55.3.013</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -4892,40 +4890,42 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>RCP 시나리오 기반 농업용 저수지의 내한능력 평가</t>
+          <t>Regional Drought Assessment Considering Climate Change and Relationship with Agricultural Water in Jeju Island</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>박나영, 최진용, 유승환, 이상현</t>
+          <t>Sung‐Ho Song, Seung‐Hwan Yoo, Seung-Jong Bae</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="n">
-        <v>55</v>
+          <t>Journal of Environmental Science International</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>13-24</t>
+          <t>625-638</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2013.55.3.013</t>
+          <t>10.5322/jesi.2013.22.5.625</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>수집 학회지</t>
+          <t>국내 기타</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -4934,7 +4934,7 @@
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M82" s="2" t="inlineStr"/>
     </row>
@@ -4947,42 +4947,40 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Regional Drought Assessment Considering Climate Change and Relationship with Agricultural Water in Jeju Island</t>
+          <t>둑높이기 농업용저수지의 운영기준에 따른 환경용수 방류패턴 분석</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Sung‐Ho Song, Seung‐Hwan Yoo, Seung-Jong Bae</t>
+          <t>이상현, 유승환, 박나영, 최진용</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Journal of Environmental Science International</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>55</v>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>625-638</t>
+          <t>51-62</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>10.5322/jesi.2013.22.5.625</t>
+          <t>10.5389/KSAE.2013.55.3.051</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4991,7 +4989,7 @@
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M83" s="2" t="inlineStr"/>
     </row>
@@ -5004,12 +5002,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>둑높이기 농업용저수지의 운영기준에 따른 환경용수 방류패턴 분석</t>
+          <t>수문인자추출에서의 SRTM DEM (Shuttle Radar Topography Mission Digital Elevation Model) 적용성 평가: 대동강 및 금강 지역 사례연구</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>이상현, 유승환, 박나영, 최진용</t>
+          <t>허용구, 유승환</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -5022,17 +5020,17 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>51-62</t>
+          <t>101-112</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2013.55.3.051</t>
+          <t>10.5389/KSAE.2013.55.6.101</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -5042,11 +5040,11 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>교신저자</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="inlineStr"/>
     </row>
@@ -5059,49 +5057,39 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>수문인자추출에서의 SRTM DEM (Shuttle Radar Topography Mission Digital Elevation Model) 적용성 평가: 대동강 및 금강 지역 사례연구</t>
+          <t>저소득층 노후주택 단열성능 개선(희망의 방한칸프로젝트)을 통한 효과 분석</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>허용구, 유승환</t>
+          <t>김정화, 유승환, Jong Hoon Kim, 정학근, 장성호, 장철용</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>대한설비공학회 2013년도 하계학술발표대회</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>101-112</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>10.5389/KSAE.2013.55.6.101</t>
-        </is>
-      </c>
+          <t>725-728</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>수집 학회지</t>
+          <t>국내 기타</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>교신저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr"/>
     </row>
@@ -5110,34 +5098,46 @@
         <v>85</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>저소득층 노후주택 단열성능 개선(희망의 방한칸프로젝트)을 통한 효과 분석</t>
+          <t>A decision support system for agricultural drought management using risk assessment</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>김정화, 유승환, Jong Hoon Kim, 정학근, 장성호, 장철용</t>
+          <t>Won‐Ho Nam, Jin‐Yong Choi, Seung‐Hwan Yoo, Min-Won Jang</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>대한설비공학회 2013년도 하계학술발표대회</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr"/>
-      <c r="G86" s="2" t="inlineStr"/>
+          <t>Paddy and Water Environment</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>725-728</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr"/>
+          <t>197-207</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>10.1007/s10333-012-0329-z</t>
+        </is>
+      </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M86" s="2" t="inlineStr"/>
     </row>
@@ -5159,22 +5159,22 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>A decision support system for agricultural drought management using risk assessment</t>
+          <t>A real-time online drought broadcast system for monitoring soil moisture index</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Won‐Ho Nam, Jin‐Yong Choi, Seung‐Hwan Yoo, Min-Won Jang</t>
+          <t>Won‐Ho Nam, Jin‐Yong Choi, Seung‐Hwan Yoo, Bernard A. Engel</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Paddy and Water Environment</t>
+          <t>KSCE Journal of Civil Engineering</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -5184,17 +5184,17 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>197-207</t>
+          <t>357-365</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>10.1007/s10333-012-0329-z</t>
+          <t>10.1007/s12205-012-1357-3</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>국내 기타</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="M87" s="2" t="inlineStr"/>
     </row>
@@ -5216,51 +5216,47 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>A real-time online drought broadcast system for monitoring soil moisture index</t>
+          <t>Analysis of design water requirement of paddy rice using frequency analysis affected by climate change in South Korea</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Won‐Ho Nam, Jin‐Yong Choi, Seung‐Hwan Yoo, Bernard A. Engel</t>
+          <t>Seung‐Hwan Yoo, Jin‐Yong Choi, Won‐Ho Nam, Eunmi Hong</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>KSCE Journal of Civil Engineering</t>
+          <t>Agricultural Water Management</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>357-365</t>
+          <t>33-42</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>10.1007/s12205-012-1357-3</t>
+          <t>10.1016/j.agwat.2012.06.002</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>주저자</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="M88" s="2" t="inlineStr"/>
     </row>
@@ -5273,12 +5269,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Analysis of design water requirement of paddy rice using frequency analysis affected by climate change in South Korea</t>
+          <t>Climate change impacts on water storage requirements of an agricultural reservoir considering changes in land use and rice growing season in Korea</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Seung‐Hwan Yoo, Jin‐Yong Choi, Won‐Ho Nam, Eunmi Hong</t>
+          <t>Yoo Seung-Hwan, Jin‐Yong Choi, Sang‐Hyun Lee, Yun‐Gyeong Oh, Yun Dong Koun</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -5288,18 +5284,18 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>33-42</t>
+          <t>43-54</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.agwat.2012.06.002</t>
+          <t>10.1016/j.agwat.2012.10.023</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -5313,7 +5309,7 @@
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="M89" s="2" t="inlineStr"/>
     </row>
@@ -5326,38 +5322,38 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Climate change impacts on water storage requirements of an agricultural reservoir considering changes in land use and rice growing season in Korea</t>
+          <t>Estimation of Agricultural Water and Land Required to Substitute the Import of Feed-grain for Domestic Production</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Yoo Seung-Hwan, Jin‐Yong Choi, Sang‐Hyun Lee, Yun‐Gyeong Oh, Yun Dong Koun</t>
+          <t>Seung‐Hwan Yoo, Jeongbin Im, Jin Yong Choi, Sanghyun Lee</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Agricultural Water Management</t>
+          <t>Journal of the Korean Society of International Agriculture</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr"/>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>43-54</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.agwat.2012.10.023</t>
-        </is>
-      </c>
+          <t>259-264</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>국내 기타</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -5366,7 +5362,7 @@
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="M90" s="2" t="inlineStr"/>
     </row>
@@ -5379,47 +5375,47 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Estimation of Agricultural Water and Land Required to Substitute the Import of Feed-grain for Domestic Production</t>
+          <t>Evaluating spatial centrality for integrated tourism management in rural areas using GIS and network analysis</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Seung‐Hwan Yoo, Jeongbin Im, Jin Yong Choi, Sanghyun Lee</t>
+          <t>Sang-Hyun Lee, Jin‐Yong Choi, Seung-Hwan Yoo, Yun‐Gyeong Oh</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Journal of the Korean Society of International Agriculture</t>
+          <t>Tourism Management</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>259-264</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr"/>
+          <t>14-24</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>10.1016/j.tourman.2012.03.005</t>
+        </is>
+      </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>주저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>3</v>
+        <v>144</v>
       </c>
       <c r="M91" s="2" t="inlineStr"/>
     </row>
@@ -5432,38 +5428,30 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Evaluating spatial centrality for integrated tourism management in rural areas using GIS and network analysis</t>
+          <t>가로주택정비사업 대상지 선정을 위한 서울시 공간구조 분석</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Sang-Hyun Lee, Jin‐Yong Choi, Seung-Hwan Yoo, Yun‐Gyeong Oh</t>
+          <t>임재성, 박현신, 유승환, 강준모</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Tourism Management</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+          <t>한국도시설계학회 추계학술발표대회 논문집</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>14-24</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.tourman.2012.03.005</t>
-        </is>
-      </c>
+          <t>192-199</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>국내 기타</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -5472,7 +5460,7 @@
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr"/>
     </row>
@@ -5485,39 +5473,49 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>가로주택정비사업 대상지 선정을 위한 서울시 공간구조 분석</t>
+          <t>고해상도 기후시나리오를 이용한 논용수 수요량 및 단위용수량의 기후변화 영향 분석</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>임재성, 박현신, 유승환, 강준모</t>
+          <t>유승환, 최진용, 이상현, 오윤경, 박나영</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>한국도시설계학회 추계학술발표대회 논문집</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr"/>
-      <c r="G93" s="2" t="inlineStr"/>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>192-199</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr"/>
+          <t>15-26</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>10.5389/KSAE.2012.54.2.015</t>
+        </is>
+      </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>주저자</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M93" s="2" t="inlineStr"/>
     </row>
@@ -5530,12 +5528,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>고해상도 기후시나리오를 이용한 논용수 수요량 및 단위용수량의 기후변화 영향 분석</t>
+          <t>기후변화 시나리오 (A1B)에 따른 농업용 저수지 유역의 미래 토지피복변화 예측 및 논 면적 변화 특성 분석</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>유승환, 최진용, 이상현, 오윤경, 박나영</t>
+          <t>오윤경, 유승환, 이상현, 박나영, 최진용, 윤동균</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -5553,12 +5551,12 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>15-26</t>
+          <t>77-86</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2012.54.2.015</t>
+          <t>10.5389/KSAE.2012.54.2.077</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -5568,11 +5566,11 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>주저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="M94" s="2" t="inlineStr"/>
     </row>
@@ -5585,12 +5583,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>기후변화 시나리오 (A1B)에 따른 농업용 저수지 유역의 미래 토지피복변화 예측 및 논 면적 변화 특성 분석</t>
+          <t>기후변화 시나리오에 따른 미래 논벼의 소비수량 및 생산량 변화 분석</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>오윤경, 유승환, 이상현, 박나영, 최진용, 윤동균</t>
+          <t>이태석, 최진용, 유승환, 이상현, 오윤경</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -5603,17 +5601,17 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>77-86</t>
+          <t>47-54</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2012.54.2.077</t>
+          <t>10.5389/KSAE.2012.54.1.047</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -5627,7 +5625,7 @@
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M95" s="2" t="inlineStr"/>
     </row>
@@ -5640,40 +5638,38 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>기후변화 시나리오에 따른 미래 논벼의 소비수량 및 생산량 변화 분석</t>
+          <t>기후변화의 농업환경 요인 영향을 고려한 미래 농어촌용수 수요 평가</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>이태석, 최진용, 유승환, 이상현, 오윤경</t>
+          <t>Jin-Yong Choi, 유승환, Yun Kyung Oh, 이상현, 윤동균</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="n">
-        <v>54</v>
+          <t>물과 미래 : 한국수자원학회지 = Water for future</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>47-54</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>10.5389/KSAE.2012.54.1.047</t>
-        </is>
-      </c>
+          <t>73-83</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr"/>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>수집 학회지</t>
+          <t>국내 기타</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -5682,7 +5678,7 @@
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr"/>
     </row>
@@ -5695,23 +5691,21 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>기후변화의 농업환경 요인 영향을 고려한 미래 농어촌용수 수요 평가</t>
+          <t>농업가뭄대응을 위한 가뭄기상시나리오 모델 개발 및 적용</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Jin-Yong Choi, 유승환, Yun Kyung Oh, 이상현, 윤동균</t>
+          <t>유승환, 최진용, 남원호, 김태곤, 고광돈</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>물과 미래 : 한국수자원학회지 = Water for future</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>54</v>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
@@ -5720,22 +5714,26 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>73-83</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr"/>
+          <t>67-75</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>10.5389/KSAE.2012.54.2.067</t>
+        </is>
+      </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>주저자</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M97" s="2" t="inlineStr"/>
     </row>
@@ -5748,12 +5746,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>농업가뭄대응을 위한 가뭄기상시나리오 모델 개발 및 적용</t>
+          <t>둑높이기 농업용저수지의 환경용수 방류기준 설정</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>유승환, 최진용, 남원호, 김태곤, 고광돈</t>
+          <t>유승환, 이상현, 최진용, 박태선</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -5766,17 +5764,17 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>67-75</t>
+          <t>17-24</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2012.54.2.067</t>
+          <t>10.5389/KSAE.2012.54.5.017</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -5790,7 +5788,7 @@
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M98" s="2" t="inlineStr"/>
     </row>
@@ -5803,49 +5801,39 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>둑높이기 농업용저수지의 환경용수 방류기준 설정</t>
+          <t>소형임대주택 공급을 위한 대상지 선정에 관한 기초연구</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>유승환, 이상현, 최진용, 박태선</t>
+          <t>진형석, 박현신, 유승환, 강준모</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>한국도시설계학회 추계학술발표대회 논문집</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>17-24</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>10.5389/KSAE.2012.54.5.017</t>
-        </is>
-      </c>
+          <t>260-268</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>수집 학회지</t>
+          <t>국내 기타</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>주저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M99" s="2" t="inlineStr"/>
     </row>
@@ -5858,30 +5846,40 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>소형임대주택 공급을 위한 대상지 선정에 관한 기초연구</t>
+          <t>잣나무림에서의 시기별 토층별 토양수분 특성분석</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>진형석, 박현신, 유승환, 강준모</t>
+          <t>홍은미, 최진용, 유승환, 남원호</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>한국도시설계학회 추계학술발표대회 논문집</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr"/>
-      <c r="G100" s="2" t="inlineStr"/>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>260-268</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr"/>
+          <t>105-114</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>10.5389/KSAE.2012.54.4.105</t>
+        </is>
+      </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -5890,7 +5888,7 @@
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M100" s="2" t="inlineStr"/>
     </row>
@@ -5899,53 +5897,55 @@
         <v>100</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>잣나무림에서의 시기별 토층별 토양수분 특성분석</t>
+          <t>Estimation of the international virtual water flow of grain crop products in Korea</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>홍은미, 최진용, 유승환, 남원호</t>
+          <t>Seung-Hwan Yoo, Tae‐Gon Kim, Jeong-Bin Im, Jin-Yong Choi</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="n">
-        <v>54</v>
+          <t>Paddy and Water Environment</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>105-114</t>
+          <t>83-93</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2012.54.4.105</t>
+          <t>10.1007/s10333-011-0267-1</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>수집 학회지</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>주저자</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M101" s="2" t="inlineStr"/>
     </row>
@@ -5958,51 +5958,49 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Estimation of the international virtual water flow of grain crop products in Korea</t>
+          <t>기후변화 시나리오에 따른 미래 토지피복변화 예측 및 군집분석을 이용한 지역 특성 분석</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Seung-Hwan Yoo, Tae‐Gon Kim, Jeong-Bin Im, Jin-Yong Choi</t>
+          <t>오윤경, 최진용, 유승환, 이상현</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Paddy and Water Environment</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>53</v>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>83-93</t>
+          <t>31-41</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>10.1007/s10333-011-0267-1</t>
+          <t>10.5389/KSAE.2011.53.6.031</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>주저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M102" s="2" t="inlineStr"/>
     </row>
@@ -6015,12 +6013,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>기후변화 시나리오에 따른 미래 토지피복변화 예측 및 군집분석을 이용한 지역 특성 분석</t>
+          <t>침엽수 산림에서의 토양수분 감쇄특성 분석</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>오윤경, 최진용, 유승환, 이상현</t>
+          <t>홍은미, 최진용, 남원호, 유승환</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -6033,17 +6031,17 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>31-41</t>
+          <t>1-9</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2011.53.6.031</t>
+          <t>10.5389/KSAE.2011.53.4.001</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -6057,7 +6055,7 @@
         </is>
       </c>
       <c r="L103" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M103" s="2" t="inlineStr"/>
     </row>
@@ -6066,44 +6064,46 @@
         <v>103</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>침엽수 산림에서의 토양수분 감쇄특성 분석</t>
+          <t>Prediction of paddy field change based on climate change scenarios using the CLUE model</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>홍은미, 최진용, 남원호, 유승환</t>
+          <t>Yun‐Gyeong Oh, Seung‐Hwan Yoo, Sang‐Hyun Lee, Jin‐Yong Choi</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="n">
-        <v>53</v>
+          <t>Paddy and Water Environment</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>1-9</t>
+          <t>309-323</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2011.53.4.001</t>
+          <t>10.1007/s10333-010-0244-0</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>수집 학회지</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M104" s="2" t="inlineStr"/>
     </row>
@@ -6125,42 +6125,40 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Prediction of paddy field change based on climate change scenarios using the CLUE model</t>
+          <t>바이오순환림의 저농도액비 시용에 따른 토양수 및 지하수 수질 영향 분석</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Yun‐Gyeong Oh, Seung‐Hwan Yoo, Sang‐Hyun Lee, Jin‐Yong Choi</t>
+          <t>홍은미, 최진용, 유승환, 남원호, 여진기, 최인규</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Paddy and Water Environment</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>52</v>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>309-323</t>
+          <t>37-45</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>10.1007/s10333-010-0244-0</t>
+          <t>10.5389/KSAE.2010.52.5.037</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -6169,7 +6167,7 @@
         </is>
       </c>
       <c r="L105" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="M105" s="2" t="inlineStr"/>
     </row>
@@ -6182,49 +6180,39 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>바이오순환림의 저농도액비 시용에 따른 토양수 및 지하수 수질 영향 분석</t>
+          <t>서울시 권역별 지하철 역세권 도시공간구조특성에 따른 지가 영향요인 분석</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>홍은미, 최진용, 유승환, 남원호, 여진기, 최인규</t>
+          <t>유승환, 임정수, 강준모</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>한국도시설계학회 추계학술발표대회 논문집</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>37-45</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>10.5389/KSAE.2010.52.5.037</t>
-        </is>
-      </c>
+          <t>149-159</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr"/>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>수집 학회지</t>
+          <t>국내 기타</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>주저자</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M106" s="2" t="inlineStr"/>
     </row>
@@ -6237,40 +6225,44 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>서울시 권역별 지하철 역세권 도시공간구조특성에 따른 지가 영향요인 분석</t>
+          <t>토지피복변화 예측을 위한 CLUE 모델의 확률지도 생성</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>유승환, 임정수, 강준모</t>
+          <t>오윤경, 최진용, 배승종, 유승환, 이상현</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>한국도시설계학회 추계학술발표대회 논문집</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr"/>
-      <c r="G107" s="2" t="inlineStr"/>
+          <t>농촌계획</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>149-159</t>
+          <t>47-55</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr"/>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>주저자</t>
-        </is>
-      </c>
-      <c r="L107" s="2" t="n">
-        <v>0</v>
-      </c>
+          <t>공저자</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr"/>
       <c r="M107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
@@ -6278,37 +6270,41 @@
         <v>107</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>토지피복변화 예측을 위한 CLUE 모델의 확률지도 생성</t>
+          <t>LARS-WG를 이용한 기후변화에 따른 논벼 증발산량 산정</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>오윤경, 최진용, 배승종, 유승환, 이상현</t>
+          <t>홍은미, 최진용, 이상현, 유승환, 강문성</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
+          <t>한국농공학회논문집</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>47-55</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr"/>
+          <t>25-35</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>10.5389/KSAE.2009.51.3.025</t>
+        </is>
+      </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
           <t>수집 학회지</t>
@@ -6319,7 +6315,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="n">
+        <v>25</v>
+      </c>
       <c r="M108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
@@ -6331,40 +6329,38 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>LARS-WG를 이용한 기후변화에 따른 논벼 증발산량 산정</t>
+          <t>다물체 동역학 프로그램 ADAMS를 이용한 구조 진동 해석</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>홍은미, 최진용, 이상현, 유승환, 강문성</t>
+          <t>이혁재, 유승환</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="n">
-        <v>51</v>
+          <t>기계저널</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>25-35</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t>10.5389/KSAE.2009.51.3.025</t>
-        </is>
-      </c>
+          <t>41-47</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr"/>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>수집 학회지</t>
+          <t>국내 기타</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -6373,7 +6369,7 @@
         </is>
       </c>
       <c r="L109" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M109" s="2" t="inlineStr"/>
     </row>
@@ -6386,47 +6382,49 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>다물체 동역학 프로그램 ADAMS를 이용한 구조 진동 해석</t>
+          <t>한국의 농산물 가상수 산정</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>이혁재, 유승환</t>
+          <t>유승환, 최진용, 김태곤, 임정빈, 전창후</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>기계저널</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
+          <t>한국수자원학회논문집</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>42</v>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>41-47</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr"/>
+          <t>911-920</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>10.3741/JKWRA.2009.42.11.911</t>
+        </is>
+      </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>주저자</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M110" s="2" t="inlineStr"/>
     </row>
@@ -6435,44 +6433,46 @@
         <v>110</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>한국의 농산물 가상수 산정</t>
+          <t>Estimation of design water requirement using FAO Penman–Monteith and optimal probability distribution function in South Korea</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>유승환, 최진용, 김태곤, 임정빈, 전창후</t>
+          <t>Seung‐Hwan Yoo, Jin‐Yong Choi, Min-Won Jang</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>한국수자원학회논문집</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="n">
-        <v>42</v>
+          <t>Agricultural Water Management</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>911-920</t>
+          <t>845-853</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>10.3741/JKWRA.2009.42.11.911</t>
+          <t>10.1016/j.agwat.2008.02.010</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>수집 학회지</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -6481,7 +6481,7 @@
         </is>
       </c>
       <c r="L111" s="2" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="M111" s="2" t="inlineStr"/>
     </row>
@@ -6494,51 +6494,47 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Estimation of design water requirement using FAO Penman–Monteith and optimal probability distribution function in South Korea</t>
+          <t>UWB 동기화를 위한 새로운 결정 법칙들</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Seung‐Hwan Yoo, Jin‐Yong Choi, Min-Won Jang</t>
+          <t>정다해, 이영윤, 안상호, 이의형, 유승환, 윤석호</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Agricultural Water Management</t>
+          <t>한국통신학회논문지</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>845-853</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.agwat.2008.02.010</t>
-        </is>
-      </c>
+          <t>192-199</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr"/>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>국내 기타</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>주저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M112" s="2" t="inlineStr"/>
     </row>
@@ -6551,47 +6547,49 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>UWB 동기화를 위한 새로운 결정 법칙들</t>
+          <t>북한의 지역별 기상학적 가뭄의 평가와 유형분류</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>정다해, 이영윤, 안상호, 이의형, 유승환, 윤석호</t>
+          <t>유승환, 남원호, 장민원, 최진용</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>한국통신학회논문지</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>50</v>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>192-199</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr"/>
+          <t>3-15</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>10.5389/KSAE.2008.50.4.003</t>
+        </is>
+      </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>주저자</t>
         </is>
       </c>
       <c r="L113" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M113" s="2" t="inlineStr"/>
     </row>
@@ -6604,12 +6602,12 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>북한의 지역별 기상학적 가뭄의 평가와 유형분류</t>
+          <t>북한지역에 대한 기상학적 가뭄지수의 적용</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>유승환, 남원호, 장민원, 최진용</t>
+          <t>남원호, 유승환, 장민원, 최진용</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -6622,7 +6620,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6632,7 +6630,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2008.50.4.003</t>
+          <t>10.5389/KSAE.2008.50.3.003</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -6642,11 +6640,11 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>주저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M114" s="2" t="inlineStr"/>
     </row>
@@ -6659,40 +6657,38 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>북한지역에 대한 기상학적 가뭄지수의 적용</t>
+          <t>상관 함수의 기울기 차에 기반한 GNSS의 부호 추적 기법</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>남원호, 유승환, 장민원, 최진용</t>
+          <t>유승수, 유승환, 정다해, 안상호, 윤석호, 김선용</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="n">
-        <v>50</v>
+          <t>한국통신학회논문지</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>3-15</t>
-        </is>
-      </c>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t>10.5389/KSAE.2008.50.3.003</t>
-        </is>
-      </c>
+          <t>505-511</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr"/>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>수집 학회지</t>
+          <t>국내 기타</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -6701,7 +6697,7 @@
         </is>
       </c>
       <c r="L115" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M115" s="2" t="inlineStr"/>
     </row>
@@ -6710,42 +6706,46 @@
         <v>115</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>상관 함수의 기울기 차에 기반한 GNSS의 부호 추적 기법</t>
+          <t>Electrically refreshable carbon-nanotube-based gas sensors</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>유승수, 유승환, 정다해, 안상호, 윤석호, 김선용</t>
+          <t>Young Wook Chang, Je Seung Oh, Seung Hwan Yoo, Hyang Hee Choi, Kyung‐Hwa Yoo</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>한국통신학회논문지</t>
+          <t>Nanotechnology</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>43</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>505-511</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="inlineStr"/>
+          <t>435504</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>10.1088/0957-4484/18/43/435504</t>
+        </is>
+      </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M116" s="2" t="inlineStr"/>
     </row>
@@ -6767,39 +6767,23 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Electrically refreshable carbon-nanotube-based gas sensors</t>
+          <t>Gas sensors based on single-wall carbon nanotubes and polypyrrole-coated carbon nanotubes</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Young Wook Chang, Je Seung Oh, Seung Hwan Yoo, Hyang Hee Choi, Kyung‐Hwa Yoo</t>
+          <t>Young Wook Chang, Je Seung Oh, Seung Hwan Yoo, Ji Hun Kim, Hyang Hee Choi, Kyung-Hwa Yoo</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Nanotechnology</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>435504</t>
-        </is>
-      </c>
-      <c r="I117" s="2" t="inlineStr">
-        <is>
-          <t>10.1088/0957-4484/18/43/435504</t>
-        </is>
-      </c>
+          <t>Bulletin of the American Physical Society</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr"/>
+      <c r="I117" s="2" t="inlineStr"/>
       <c r="J117" s="2" t="inlineStr">
         <is>
           <t>해외</t>
@@ -6811,7 +6795,7 @@
         </is>
       </c>
       <c r="L117" s="2" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M117" s="2" t="inlineStr"/>
     </row>
@@ -6824,26 +6808,40 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Gas sensors based on single-wall carbon nanotubes and polypyrrole-coated carbon nanotubes</t>
+          <t>NOAA/AVHRR NDVI를 이용한 북한지역 봄 가뭄 분석</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Young Wook Chang, Je Seung Oh, Seung Hwan Yoo, Ji Hun Kim, Hyang Hee Choi, Kyung-Hwa Yoo</t>
+          <t>장민원, 유승환, 최진용</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Bulletin of the American Physical Society</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr"/>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr"/>
-      <c r="I118" s="2" t="inlineStr"/>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>21-33</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>10.5389/KSAE.2007.49.6.021</t>
+        </is>
+      </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -6852,7 +6850,7 @@
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M118" s="2" t="inlineStr"/>
     </row>
@@ -6865,12 +6863,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>NOAA/AVHRR NDVI를 이용한 북한지역 봄 가뭄 분석</t>
+          <t>빈도 분석법을 이용한 논벼의 한발 기준 10년 빈도 작물 증발산량 산정</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>장민원, 유승환, 최진용</t>
+          <t>유승환, 최진용, 장민원</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -6883,17 +6881,17 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>21-33</t>
+          <t>11-20</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2007.49.6.021</t>
+          <t>10.5389/KSAE.2007.49.3.011</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
@@ -6903,11 +6901,11 @@
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>주저자</t>
         </is>
       </c>
       <c r="L119" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M119" s="2" t="inlineStr"/>
     </row>
@@ -6920,12 +6918,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>빈도 분석법을 이용한 논벼의 한발 기준 10년 빈도 작물 증발산량 산정</t>
+          <t>시계열 MODIS 영상을 이용한 논 분류와 지형학적 인자에 따른 불확실성 분석</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>유승환, 최진용, 장민원</t>
+          <t>윤성한, 최진용, 유승환, 장민원</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -6938,17 +6936,17 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>11-20</t>
+          <t>67-77</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2007.49.3.011</t>
+          <t>10.5389/KSAE.2007.49.5.067</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -6958,11 +6956,11 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>주저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M120" s="2" t="inlineStr"/>
     </row>
@@ -6971,16 +6969,16 @@
         <v>120</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>시계열 MODIS 영상을 이용한 논 분류와 지형학적 인자에 따른 불확실성 분석</t>
+          <t>논벼에 대한 Penman-Monteith와 FAO Modified Penman 공식의 작물 계수 산정</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>윤성한, 최진용, 유승환, 장민원</t>
+          <t>유승환, 최진용, 장민원</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -6989,21 +6987,21 @@
         </is>
       </c>
       <c r="F121" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>67-77</t>
+          <t>13-23</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2007.49.5.067</t>
+          <t>10.5389/KSAE.2006.48.1.013</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
@@ -7013,11 +7011,11 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>주저자</t>
         </is>
       </c>
       <c r="L121" s="2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M121" s="2" t="inlineStr"/>
     </row>
@@ -7030,38 +7028,40 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>A Scheme of Distributed Network Security Management against DDoS Attacks</t>
+          <t>토양수분지수를 이용한 유역단위 가뭄 평가</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Kim Sung-Ki, Yoo Seung-Hwan, Kim Moon-Chan, Min Byoung-Joon</t>
+          <t>김옥경, 최진용, 장민원, 유승환, 남원호, 이주헌, 노재경</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Journal of the Institute of Electronics Engineers of Korea</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>48</v>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>72-83</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="inlineStr"/>
+          <t>3-13</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>10.5389/KSAE.2006.48.6.003</t>
+        </is>
+      </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>해외</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M122" s="2" t="inlineStr"/>
     </row>
@@ -7079,44 +7079,34 @@
         <v>122</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>논벼에 대한 Penman-Monteith와 FAO Modified Penman 공식의 작물 계수 산정</t>
+          <t>보행형 이동 로봇의 동적 걸음 계획</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>유승환, 최진용, 장민원</t>
+          <t>유승환, 김정훈, 김영배</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>한국정밀공학회 학술발표대회 논문집</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr"/>
+      <c r="G123" s="2" t="inlineStr"/>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>13-23</t>
-        </is>
-      </c>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t>10.5389/KSAE.2006.48.1.013</t>
-        </is>
-      </c>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr"/>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>수집 학회지</t>
+          <t>국내 기타</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -7125,7 +7115,7 @@
         </is>
       </c>
       <c r="L123" s="2" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M123" s="2" t="inlineStr"/>
     </row>
@@ -7134,53 +7124,43 @@
         <v>123</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>토양수분지수를 이용한 유역단위 가뭄 평가</t>
+          <t>송변전분야 IT 적용사례 및 전망</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>김옥경, 최진용, 장민원, 유승환, 남원호, 이주헌, 노재경</t>
+          <t>유승환, 정종갑</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>전기저널</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr"/>
+      <c r="G124" s="2" t="inlineStr"/>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>3-13</t>
-        </is>
-      </c>
-      <c r="I124" s="2" t="inlineStr">
-        <is>
-          <t>10.5389/KSAE.2006.48.6.003</t>
-        </is>
-      </c>
+          <t>30-38</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr"/>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>수집 학회지</t>
+          <t>국내 기타</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
+          <t>주저자</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M124" s="2" t="inlineStr"/>
     </row>
@@ -7189,16 +7169,16 @@
         <v>124</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>2005</v>
+        <v>2001</v>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>보행형 이동 로봇의 동적 걸음 계획</t>
+          <t>ADAMS를 이용한 다축 시뮬레이터에 관한 연구</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>유승환, 김정훈, 김영배</t>
+          <t>정찬범, 유승환, 이경백, 김영배</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -7210,7 +7190,7 @@
       <c r="G125" s="2" t="inlineStr"/>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>288-291</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr"/>
@@ -7221,103 +7201,13 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>주저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L125" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M125" s="2" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="n">
-        <v>125</v>
-      </c>
-      <c r="B126" s="2" t="n">
-        <v>2005</v>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>송변전분야 IT 적용사례 및 전망</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>유승환, 정종갑</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>전기저널</t>
-        </is>
-      </c>
-      <c r="F126" s="2" t="inlineStr"/>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>30-38</t>
-        </is>
-      </c>
-      <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>국내 기타</t>
-        </is>
-      </c>
-      <c r="K126" s="2" t="inlineStr">
-        <is>
-          <t>주저자</t>
-        </is>
-      </c>
-      <c r="L126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" s="2" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="n">
-        <v>126</v>
-      </c>
-      <c r="B127" s="2" t="n">
-        <v>2001</v>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>ADAMS를 이용한 다축 시뮬레이터에 관한 연구</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>정찬범, 유승환, 이경백, 김영배</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
-        <is>
-          <t>한국정밀공학회 학술발표대회 논문집</t>
-        </is>
-      </c>
-      <c r="F127" s="2" t="inlineStr"/>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>288-291</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="inlineStr"/>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>국내 기타</t>
-        </is>
-      </c>
-      <c r="K127" s="2" t="inlineStr">
-        <is>
-          <t>공저자</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
